--- a/data/source/weekly/cs-en-us-005pct.xlsx
+++ b/data/source/weekly/cs-en-us-005pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -892,38 +892,38 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="15">
+      <c r="C15" s="15">
         <v>1</v>
       </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="15">
         <v>2</v>
       </c>
       <c r="K15" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M15" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N15" s="14">
         <v>0</v>
@@ -943,31 +943,31 @@
         <v>-100</v>
       </c>
       <c r="F16" s="15">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G16" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H16" s="14">
+        <v>-28.571428571428</v>
+      </c>
+      <c r="I16" s="15">
+        <v>20</v>
+      </c>
+      <c r="J16" s="15">
+        <v>14</v>
+      </c>
+      <c r="K16" s="14">
+        <v>42.857142857142</v>
+      </c>
+      <c r="L16" s="14">
         <v>66.666666666666</v>
       </c>
-      <c r="I16" s="15">
-        <v>21</v>
-      </c>
-      <c r="J16" s="15">
-        <v>13</v>
-      </c>
-      <c r="K16" s="14">
-        <v>61.538461538461</v>
-      </c>
-      <c r="L16" s="14">
-        <v>110</v>
-      </c>
       <c r="M16" s="14">
-        <v>61.538461538461</v>
+        <v>53.846153846153</v>
       </c>
       <c r="N16" s="14">
-        <v>-64.406779661017</v>
+        <v>-72.602739726027</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D17" s="15">
         <v>3</v>
       </c>
       <c r="E17" s="14">
-        <v>33.333333333333</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F17" s="15">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G17" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H17" s="14">
-        <v>122.222222222222</v>
+        <v>58.333333333333</v>
       </c>
       <c r="I17" s="15">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J17" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K17" s="14">
-        <v>118.181818181818</v>
+        <v>121.428571428571</v>
       </c>
       <c r="L17" s="14">
-        <v>4.347826086956</v>
+        <v>3.333333333333</v>
       </c>
       <c r="M17" s="14">
-        <v>166.666666666667</v>
+        <v>158.333333333333</v>
       </c>
       <c r="N17" s="14">
-        <v>14.285714285714</v>
+        <v>34.782608695652</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>4</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+        <v>6</v>
+      </c>
+      <c r="D18" s="15">
+        <v>5</v>
+      </c>
+      <c r="E18" s="14">
+        <v>20</v>
       </c>
       <c r="F18" s="15">
+        <v>16</v>
+      </c>
+      <c r="G18" s="15">
+        <v>10</v>
+      </c>
+      <c r="H18" s="14">
+        <v>60</v>
+      </c>
+      <c r="I18" s="15">
+        <v>24</v>
+      </c>
+      <c r="J18" s="15">
         <v>13</v>
       </c>
-      <c r="G18" s="15">
-        <v>6</v>
-      </c>
-      <c r="H18" s="14">
-        <v>116.666666666667</v>
-      </c>
-      <c r="I18" s="15">
-        <v>18</v>
-      </c>
-      <c r="J18" s="15">
-        <v>8</v>
-      </c>
       <c r="K18" s="14">
-        <v>125</v>
+        <v>84.615384615384</v>
       </c>
       <c r="L18" s="14">
-        <v>38.461538461538</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M18" s="14">
-        <v>-10</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="N18" s="14">
-        <v>-82.352941176470</v>
+        <v>-77.777777777777</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D19" s="15">
         <v>13</v>
       </c>
       <c r="E19" s="14">
-        <v>-7.692307692307</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="F19" s="15">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="G19" s="15">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H19" s="14">
-        <v>-14.035087719298</v>
+        <v>-19.607843137254</v>
       </c>
       <c r="I19" s="15">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="J19" s="15">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K19" s="14">
-        <v>-6.493506493506</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L19" s="14">
-        <v>-18.181818181818</v>
+        <v>-21.568627450980</v>
       </c>
       <c r="M19" s="14">
-        <v>20</v>
+        <v>21.212121212121</v>
       </c>
       <c r="N19" s="14">
-        <v>-55</v>
+        <v>-56.521739130434</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,7 +1101,7 @@
         <v>20</v>
       </c>
       <c r="D20" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="14">
         <v>-100</v>
@@ -1110,19 +1110,19 @@
         <v>1</v>
       </c>
       <c r="G20" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H20" s="14">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="I20" s="15">
         <v>1</v>
       </c>
       <c r="J20" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K20" s="14">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="L20" s="14">
         <v>-85.714285714285</v>
@@ -1131,7 +1131,7 @@
         <v>-50</v>
       </c>
       <c r="N20" s="14">
-        <v>-97.727272727272</v>
+        <v>-98.181818181818</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D21" s="17">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>5.263157894736</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="G21" s="17">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H21" s="18">
-        <v>17.857142857142</v>
+        <v>-1.176470588235</v>
       </c>
       <c r="I21" s="17">
+        <v>158</v>
+      </c>
+      <c r="J21" s="17">
         <v>137</v>
       </c>
-      <c r="J21" s="17">
-        <v>113</v>
-      </c>
       <c r="K21" s="18">
-        <v>21.238938053097</v>
+        <v>15.328467153284</v>
       </c>
       <c r="L21" s="18">
-        <v>-2.836879432624</v>
+        <v>-8.139534883720</v>
       </c>
       <c r="M21" s="18">
-        <v>30.476190476190</v>
+        <v>31.666666666666</v>
       </c>
       <c r="N21" s="18">
-        <v>-64.690721649484</v>
+        <v>-64.573991031390</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F22" s="15">
         <v>8</v>
       </c>
       <c r="G22" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H22" s="14">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="I22" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J22" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K22" s="14">
-        <v>140</v>
+        <v>116.666666666667</v>
       </c>
       <c r="L22" s="14">
-        <v>50</v>
+        <v>44.444444444444</v>
       </c>
       <c r="M22" s="14">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="15">
+        <v>2</v>
       </c>
       <c r="D23" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F23" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G23" s="15">
+        <v>6</v>
+      </c>
+      <c r="H23" s="14">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="I23" s="15">
         <v>5</v>
       </c>
-      <c r="H23" s="14">
-        <v>-60</v>
-      </c>
-      <c r="I23" s="15">
-        <v>3</v>
-      </c>
       <c r="J23" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K23" s="14">
-        <v>-50</v>
+        <v>-37.5</v>
       </c>
       <c r="L23" s="14">
-        <v>0</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M23" s="14">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D24" s="15">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E24" s="14">
-        <v>-7.692307692307</v>
+        <v>42.857142857142</v>
       </c>
       <c r="F24" s="15">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G24" s="15">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="H24" s="14">
-        <v>-36.220472440944</v>
+        <v>-20.909090909090</v>
       </c>
       <c r="I24" s="15">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="J24" s="15">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="K24" s="14">
-        <v>-35.714285714285</v>
+        <v>-26.984126984127</v>
       </c>
       <c r="L24" s="14">
-        <v>-18.796992481203</v>
+        <v>-19.298245614035</v>
       </c>
       <c r="M24" s="14">
-        <v>-10</v>
+        <v>1.470588235294</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D25" s="15">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E25" s="14">
-        <v>5.555555555555</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="F25" s="15">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G25" s="15">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="H25" s="14">
-        <v>-37.623762376237</v>
+        <v>-31.395348837209</v>
       </c>
       <c r="I25" s="15">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="J25" s="15">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="K25" s="14">
-        <v>-38.931297709923</v>
+        <v>-35.135135135135</v>
       </c>
       <c r="L25" s="14">
-        <v>-27.927927927927</v>
+        <v>-34.693877551020</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
+        <v>13</v>
+      </c>
+      <c r="D26" s="15">
         <v>9</v>
       </c>
-      <c r="D26" s="15">
-        <v>6</v>
-      </c>
       <c r="E26" s="14">
-        <v>50</v>
+        <v>44.444444444444</v>
       </c>
       <c r="F26" s="15">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G26" s="15">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H26" s="14">
-        <v>-11.538461538461</v>
+        <v>3.225806451612</v>
       </c>
       <c r="I26" s="15">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="J26" s="15">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="K26" s="14">
-        <v>-2.941176470588</v>
+        <v>9.302325581395</v>
       </c>
       <c r="L26" s="14">
-        <v>-17.5</v>
+        <v>0</v>
       </c>
       <c r="M26" s="14">
-        <v>32</v>
+        <v>67.857142857142</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="15">
-        <v>1</v>
-      </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I27" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J27" s="15">
         <v>2</v>
       </c>
       <c r="K27" s="14">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="L27" s="14">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>1</v>
-      </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G28" s="15">
         <v>3</v>
       </c>
       <c r="H28" s="14">
-        <v>33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I28" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J28" s="15">
         <v>3</v>
       </c>
       <c r="K28" s="14">
-        <v>200</v>
+        <v>266.666666666667</v>
       </c>
       <c r="L28" s="14">
-        <v>28.571428571428</v>
+        <v>57.142857142857</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="15">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1566,8 +1566,8 @@
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="15">
-        <v>1</v>
+      <c r="I31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1575,8 +1575,8 @@
       <c r="K31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L31" s="13" t="s">
-        <v>21</v>
+      <c r="L31" s="14">
+        <v>-100</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-005pct.xlsx
+++ b/data/source/weekly/cs-en-us-005pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -892,32 +892,32 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="15">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="15">
+        <v>1</v>
+      </c>
+      <c r="G15" s="15">
         <v>2</v>
       </c>
-      <c r="G15" s="15">
-        <v>1</v>
-      </c>
       <c r="H15" s="14">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="15">
         <v>2</v>
       </c>
       <c r="J15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>21</v>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="15">
+        <v>2</v>
       </c>
       <c r="D16" s="15">
         <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F16" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H16" s="14">
-        <v>-28.571428571428</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I16" s="15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J16" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K16" s="14">
-        <v>42.857142857142</v>
+        <v>46.666666666666</v>
       </c>
       <c r="L16" s="14">
-        <v>66.666666666666</v>
+        <v>69.230769230769</v>
       </c>
       <c r="M16" s="14">
-        <v>53.846153846153</v>
+        <v>57.142857142857</v>
       </c>
       <c r="N16" s="14">
-        <v>-72.602739726027</v>
+        <v>-74.418604651162</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D17" s="15">
         <v>3</v>
       </c>
       <c r="E17" s="14">
-        <v>166.666666666667</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="15">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G17" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H17" s="14">
-        <v>58.333333333333</v>
+        <v>30.769230769230</v>
       </c>
       <c r="I17" s="15">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J17" s="15">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K17" s="14">
-        <v>121.428571428571</v>
+        <v>94.117647058823</v>
       </c>
       <c r="L17" s="14">
-        <v>3.333333333333</v>
+        <v>3.125</v>
       </c>
       <c r="M17" s="14">
-        <v>158.333333333333</v>
+        <v>94.117647058823</v>
       </c>
       <c r="N17" s="14">
-        <v>34.782608695652</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D18" s="15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E18" s="14">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F18" s="15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G18" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H18" s="14">
-        <v>60</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I18" s="15">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J18" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K18" s="14">
-        <v>84.615384615384</v>
+        <v>80</v>
       </c>
       <c r="L18" s="14">
-        <v>14.285714285714</v>
+        <v>17.391304347826</v>
       </c>
       <c r="M18" s="14">
-        <v>-7.692307692307</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="N18" s="14">
-        <v>-77.777777777777</v>
+        <v>-78.225806451612</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D19" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E19" s="14">
-        <v>-46.153846153846</v>
+        <v>21.428571428571</v>
       </c>
       <c r="F19" s="15">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G19" s="15">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H19" s="14">
-        <v>-19.607843137254</v>
+        <v>-8</v>
       </c>
       <c r="I19" s="15">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="J19" s="15">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="K19" s="14">
-        <v>-11.111111111111</v>
+        <v>-6.730769230769</v>
       </c>
       <c r="L19" s="14">
-        <v>-21.568627450980</v>
+        <v>-13.392857142857</v>
       </c>
       <c r="M19" s="14">
-        <v>21.212121212121</v>
+        <v>18.292682926829</v>
       </c>
       <c r="N19" s="14">
-        <v>-56.521739130434</v>
+        <v>-51.980198019802</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,7 +1101,7 @@
         <v>20</v>
       </c>
       <c r="D20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="14">
         <v>-100</v>
@@ -1110,19 +1110,19 @@
         <v>1</v>
       </c>
       <c r="G20" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H20" s="14">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="I20" s="15">
         <v>1</v>
       </c>
       <c r="J20" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K20" s="14">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="L20" s="14">
         <v>-85.714285714285</v>
@@ -1131,7 +1131,7 @@
         <v>-50</v>
       </c>
       <c r="N20" s="14">
-        <v>-98.181818181818</v>
+        <v>-98.305084745762</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,13 +1139,13 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>24</v>
+      </c>
+      <c r="D21" s="17">
         <v>22</v>
       </c>
-      <c r="D21" s="17">
-        <v>24</v>
-      </c>
       <c r="E21" s="18">
-        <v>-8.333333333333</v>
+        <v>9.090909090909</v>
       </c>
       <c r="F21" s="17">
         <v>84</v>
@@ -1157,60 +1157,60 @@
         <v>-1.176470588235</v>
       </c>
       <c r="I21" s="17">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="J21" s="17">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="K21" s="18">
-        <v>15.328467153284</v>
+        <v>14.465408805031</v>
       </c>
       <c r="L21" s="18">
-        <v>-8.139534883720</v>
+        <v>-2.673796791443</v>
       </c>
       <c r="M21" s="18">
-        <v>31.666666666666</v>
+        <v>25.517241379310</v>
       </c>
       <c r="N21" s="18">
-        <v>-64.573991031390</v>
+        <v>-63.888888888888</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G22" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H22" s="14">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="I22" s="15">
         <v>13</v>
       </c>
       <c r="J22" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K22" s="14">
-        <v>116.666666666667</v>
+        <v>62.5</v>
       </c>
       <c r="L22" s="14">
-        <v>44.444444444444</v>
+        <v>30</v>
       </c>
       <c r="M22" s="14">
-        <v>550</v>
+        <v>225</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,14 +1220,14 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>2</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="15">
         <v>4</v>
@@ -1242,16 +1242,16 @@
         <v>5</v>
       </c>
       <c r="J23" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K23" s="14">
-        <v>-37.5</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="L23" s="14">
         <v>-28.571428571428</v>
       </c>
       <c r="M23" s="14">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D24" s="15">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E24" s="14">
-        <v>42.857142857142</v>
+        <v>62.5</v>
       </c>
       <c r="F24" s="15">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G24" s="15">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="H24" s="14">
-        <v>-20.909090909090</v>
+        <v>7.865168539325</v>
       </c>
       <c r="I24" s="15">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="J24" s="15">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="K24" s="14">
-        <v>-26.984126984127</v>
+        <v>-20.487804878048</v>
       </c>
       <c r="L24" s="14">
-        <v>-19.298245614035</v>
+        <v>-13.756613756613</v>
       </c>
       <c r="M24" s="14">
-        <v>1.470588235294</v>
+        <v>5.844155844155</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D25" s="15">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E25" s="14">
-        <v>-5.882352941176</v>
+        <v>111.111111111111</v>
       </c>
       <c r="F25" s="15">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="G25" s="15">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="H25" s="14">
-        <v>-31.395348837209</v>
+        <v>6.349206349206</v>
       </c>
       <c r="I25" s="15">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="J25" s="15">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="K25" s="14">
-        <v>-35.135135135135</v>
+        <v>-26.751592356687</v>
       </c>
       <c r="L25" s="14">
-        <v>-34.693877551020</v>
+        <v>-29.447852760736</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D26" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E26" s="14">
-        <v>44.444444444444</v>
+        <v>-50</v>
       </c>
       <c r="F26" s="15">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G26" s="15">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H26" s="14">
-        <v>3.225806451612</v>
+        <v>3.448275862068</v>
       </c>
       <c r="I26" s="15">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J26" s="15">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="K26" s="14">
-        <v>9.302325581395</v>
+        <v>0</v>
       </c>
       <c r="L26" s="14">
-        <v>0</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="M26" s="14">
-        <v>67.857142857142</v>
+        <v>59.375</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F27" s="15">
+        <v>3</v>
+      </c>
+      <c r="G27" s="15">
         <v>2</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="15">
-        <v>4</v>
-      </c>
-      <c r="G27" s="15">
-        <v>1</v>
-      </c>
       <c r="H27" s="14">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="I27" s="15">
         <v>5</v>
       </c>
       <c r="J27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" s="14">
-        <v>150</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L27" s="14">
         <v>150</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>2</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="15">
+        <v>3</v>
+      </c>
+      <c r="E28" s="14">
+        <v>-66.666666666666</v>
       </c>
       <c r="F28" s="15">
+        <v>4</v>
+      </c>
+      <c r="G28" s="15">
+        <v>5</v>
+      </c>
+      <c r="H28" s="14">
+        <v>-20</v>
+      </c>
+      <c r="I28" s="15">
+        <v>12</v>
+      </c>
+      <c r="J28" s="15">
         <v>6</v>
       </c>
-      <c r="G28" s="15">
-        <v>3</v>
-      </c>
-      <c r="H28" s="14">
+      <c r="K28" s="14">
         <v>100</v>
       </c>
-      <c r="I28" s="15">
-        <v>11</v>
-      </c>
-      <c r="J28" s="15">
-        <v>3</v>
-      </c>
-      <c r="K28" s="14">
-        <v>266.666666666667</v>
-      </c>
       <c r="L28" s="14">
-        <v>57.142857142857</v>
+        <v>71.428571428571</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-005pct.xlsx
+++ b/data/source/weekly/cs-en-us-005pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
         <v>1</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" s="15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E16" s="14">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G16" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H16" s="14">
         <v>-33.333333333333</v>
       </c>
       <c r="I16" s="15">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J16" s="15">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K16" s="14">
-        <v>46.666666666666</v>
+        <v>23.809523809523</v>
       </c>
       <c r="L16" s="14">
-        <v>69.230769230769</v>
+        <v>85.714285714285</v>
       </c>
       <c r="M16" s="14">
-        <v>57.142857142857</v>
+        <v>62.5</v>
       </c>
       <c r="N16" s="14">
-        <v>-74.418604651162</v>
+        <v>-74.757281553398</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
+        <v>1</v>
+      </c>
+      <c r="D17" s="15">
         <v>2</v>
       </c>
-      <c r="D17" s="15">
-        <v>3</v>
-      </c>
       <c r="E17" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="15">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G17" s="15">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H17" s="14">
-        <v>30.769230769230</v>
+        <v>27.272727272727</v>
       </c>
       <c r="I17" s="15">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J17" s="15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K17" s="14">
-        <v>94.117647058823</v>
+        <v>78.947368421052</v>
       </c>
       <c r="L17" s="14">
-        <v>3.125</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="M17" s="14">
-        <v>94.117647058823</v>
+        <v>78.947368421052</v>
       </c>
       <c r="N17" s="14">
-        <v>10</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="14">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="F18" s="15">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G18" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H18" s="14">
-        <v>66.666666666666</v>
+        <v>137.5</v>
       </c>
       <c r="I18" s="15">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J18" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K18" s="14">
-        <v>80</v>
+        <v>106.25</v>
       </c>
       <c r="L18" s="14">
-        <v>17.391304347826</v>
+        <v>10</v>
       </c>
       <c r="M18" s="14">
-        <v>-6.896551724137</v>
+        <v>-2.941176470588</v>
       </c>
       <c r="N18" s="14">
-        <v>-78.225806451612</v>
+        <v>-75.912408759124</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
+        <v>15</v>
+      </c>
+      <c r="D19" s="15">
         <v>17</v>
       </c>
-      <c r="D19" s="15">
-        <v>14</v>
-      </c>
       <c r="E19" s="14">
-        <v>21.428571428571</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="F19" s="15">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G19" s="15">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="H19" s="14">
-        <v>-8</v>
+        <v>-8.771929824561</v>
       </c>
       <c r="I19" s="15">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="J19" s="15">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="K19" s="14">
-        <v>-6.730769230769</v>
+        <v>-6.611570247933</v>
       </c>
       <c r="L19" s="14">
-        <v>-13.392857142857</v>
+        <v>-12.403100775193</v>
       </c>
       <c r="M19" s="14">
-        <v>18.292682926829</v>
+        <v>25.555555555555</v>
       </c>
       <c r="N19" s="14">
-        <v>-51.980198019802</v>
+        <v>-49.553571428571</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,20 +1100,20 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="15">
-        <v>1</v>
-      </c>
-      <c r="E20" s="14">
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" s="15">
+        <v>4</v>
+      </c>
+      <c r="H20" s="14">
         <v>-100</v>
-      </c>
-      <c r="F20" s="15">
-        <v>1</v>
-      </c>
-      <c r="G20" s="15">
-        <v>5</v>
-      </c>
-      <c r="H20" s="14">
-        <v>-80</v>
       </c>
       <c r="I20" s="15">
         <v>1</v>
@@ -1125,13 +1125,13 @@
         <v>-80</v>
       </c>
       <c r="L20" s="14">
-        <v>-85.714285714285</v>
+        <v>-87.5</v>
       </c>
       <c r="M20" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N20" s="14">
-        <v>-98.305084745762</v>
+        <v>-98.507462686567</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,37 +1142,37 @@
         <v>24</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E21" s="18">
-        <v>9.090909090909</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="F21" s="17">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G21" s="17">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H21" s="18">
-        <v>-1.176470588235</v>
+        <v>1.098901098901</v>
       </c>
       <c r="I21" s="17">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="J21" s="17">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="K21" s="18">
-        <v>14.465408805031</v>
+        <v>12.972972972973</v>
       </c>
       <c r="L21" s="18">
-        <v>-2.673796791443</v>
+        <v>-3.686635944700</v>
       </c>
       <c r="M21" s="18">
-        <v>25.517241379310</v>
+        <v>28.220858895705</v>
       </c>
       <c r="N21" s="18">
-        <v>-63.888888888888</v>
+        <v>-63.588850174216</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,34 +1183,34 @@
         <v>20</v>
       </c>
       <c r="D22" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E22" s="14">
         <v>-100</v>
       </c>
       <c r="F22" s="15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G22" s="15">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H22" s="14">
-        <v>40</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="I22" s="15">
         <v>13</v>
       </c>
       <c r="J22" s="15">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K22" s="14">
-        <v>62.5</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L22" s="14">
         <v>30</v>
       </c>
       <c r="M22" s="14">
-        <v>225</v>
+        <v>116.666666666667</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="15">
-        <v>1</v>
-      </c>
-      <c r="E23" s="14">
-        <v>-100</v>
+      <c r="C23" s="15">
+        <v>2</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="15">
+        <v>5</v>
+      </c>
+      <c r="G23" s="15">
         <v>4</v>
       </c>
-      <c r="G23" s="15">
-        <v>6</v>
-      </c>
       <c r="H23" s="14">
-        <v>-33.333333333333</v>
+        <v>25</v>
       </c>
       <c r="I23" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J23" s="15">
         <v>9</v>
       </c>
       <c r="K23" s="14">
-        <v>-44.444444444444</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L23" s="14">
-        <v>-28.571428571428</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="M23" s="14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D24" s="15">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E24" s="14">
-        <v>62.5</v>
+        <v>46.153846153846</v>
       </c>
       <c r="F24" s="15">
         <v>96</v>
       </c>
       <c r="G24" s="15">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="H24" s="14">
-        <v>7.865168539325</v>
+        <v>26.315789473684</v>
       </c>
       <c r="I24" s="15">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="J24" s="15">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="K24" s="14">
-        <v>-20.487804878048</v>
+        <v>-17.431192660550</v>
       </c>
       <c r="L24" s="14">
-        <v>-13.756613756613</v>
+        <v>-20</v>
       </c>
       <c r="M24" s="14">
-        <v>5.844155844155</v>
+        <v>11.111111111111</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D25" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E25" s="14">
-        <v>111.111111111111</v>
+        <v>27.272727272727</v>
       </c>
       <c r="F25" s="15">
         <v>67</v>
       </c>
       <c r="G25" s="15">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="H25" s="14">
-        <v>6.349206349206</v>
+        <v>21.818181818181</v>
       </c>
       <c r="I25" s="15">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="J25" s="15">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="K25" s="14">
-        <v>-26.751592356687</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="L25" s="14">
-        <v>-29.447852760736</v>
+        <v>-33.678756476683</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D26" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E26" s="14">
-        <v>-50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F26" s="15">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G26" s="15">
         <v>29</v>
       </c>
       <c r="H26" s="14">
-        <v>3.448275862068</v>
+        <v>27.586206896551</v>
       </c>
       <c r="I26" s="15">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="J26" s="15">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="K26" s="14">
-        <v>0</v>
+        <v>7.017543859649</v>
       </c>
       <c r="L26" s="14">
-        <v>-5.555555555555</v>
+        <v>5.172413793103</v>
       </c>
       <c r="M26" s="14">
-        <v>59.375</v>
+        <v>69.444444444444</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="15">
+      <c r="C27" s="15">
         <v>1</v>
       </c>
-      <c r="E27" s="14">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27" s="15">
         <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I27" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J27" s="15">
         <v>3</v>
       </c>
       <c r="K27" s="14">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="L27" s="14">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
+        <v>2</v>
+      </c>
+      <c r="D28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="15">
-        <v>3</v>
-      </c>
       <c r="E28" s="14">
-        <v>-66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="F28" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G28" s="15">
         <v>5</v>
       </c>
       <c r="H28" s="14">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="I28" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J28" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K28" s="14">
         <v>100</v>
       </c>
       <c r="L28" s="14">
-        <v>71.428571428571</v>
+        <v>75</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="15">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="15">
+        <v>1</v>
+      </c>
+      <c r="H31" s="14">
+        <v>-100</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+      <c r="J31" s="15">
+        <v>1</v>
+      </c>
+      <c r="K31" s="14">
+        <v>-100</v>
       </c>
       <c r="L31" s="14">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-005pct.xlsx
+++ b/data/source/weekly/cs-en-us-005pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -905,10 +905,10 @@
         <v>1</v>
       </c>
       <c r="G15" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I15" s="15">
         <v>2</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G16" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H16" s="14">
-        <v>-33.333333333333</v>
+        <v>-30</v>
       </c>
       <c r="I16" s="15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J16" s="15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K16" s="14">
-        <v>23.809523809523</v>
+        <v>17.391304347826</v>
       </c>
       <c r="L16" s="14">
-        <v>85.714285714285</v>
+        <v>80</v>
       </c>
       <c r="M16" s="14">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="N16" s="14">
-        <v>-74.757281553398</v>
+        <v>-76.724137931034</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D17" s="15">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E17" s="14">
-        <v>-50</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F17" s="15">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G17" s="15">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H17" s="14">
-        <v>27.272727272727</v>
+        <v>13.333333333333</v>
       </c>
       <c r="I17" s="15">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="J17" s="15">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="K17" s="14">
-        <v>78.947368421052</v>
+        <v>53.846153846153</v>
       </c>
       <c r="L17" s="14">
-        <v>-5.555555555555</v>
+        <v>-2.439024390243</v>
       </c>
       <c r="M17" s="14">
-        <v>78.947368421052</v>
+        <v>100</v>
       </c>
       <c r="N17" s="14">
-        <v>-15</v>
+        <v>-4.761904761904</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1018,11 +1018,11 @@
       <c r="C18" s="15">
         <v>4</v>
       </c>
-      <c r="D18" s="15">
-        <v>1</v>
-      </c>
-      <c r="E18" s="14">
-        <v>300</v>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="15">
         <v>19</v>
@@ -1034,22 +1034,22 @@
         <v>137.5</v>
       </c>
       <c r="I18" s="15">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J18" s="15">
         <v>16</v>
       </c>
       <c r="K18" s="14">
-        <v>106.25</v>
+        <v>131.25</v>
       </c>
       <c r="L18" s="14">
-        <v>10</v>
+        <v>2.777777777777</v>
       </c>
       <c r="M18" s="14">
-        <v>-2.941176470588</v>
+        <v>0</v>
       </c>
       <c r="N18" s="14">
-        <v>-75.912408759124</v>
+        <v>-74.829931972789</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D19" s="15">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E19" s="14">
-        <v>-11.764705882352</v>
+        <v>60</v>
       </c>
       <c r="F19" s="15">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G19" s="15">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="H19" s="14">
-        <v>-8.771929824561</v>
+        <v>-2.040816326530</v>
       </c>
       <c r="I19" s="15">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="J19" s="15">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="K19" s="14">
-        <v>-6.611570247933</v>
+        <v>-3.968253968253</v>
       </c>
       <c r="L19" s="14">
-        <v>-12.403100775193</v>
+        <v>-17.687074829932</v>
       </c>
       <c r="M19" s="14">
-        <v>25.555555555555</v>
+        <v>24.742268041237</v>
       </c>
       <c r="N19" s="14">
-        <v>-49.553571428571</v>
+        <v>-52.362204724409</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1110,7 +1110,7 @@
         <v>20</v>
       </c>
       <c r="G20" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H20" s="14">
         <v>-100</v>
@@ -1131,7 +1131,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N20" s="14">
-        <v>-98.507462686567</v>
+        <v>-98.666666666666</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E21" s="18">
-        <v>-7.692307692307</v>
+        <v>35.714285714285</v>
       </c>
       <c r="F21" s="17">
         <v>92</v>
       </c>
       <c r="G21" s="17">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="H21" s="18">
-        <v>1.098901098901</v>
+        <v>6.976744186046</v>
       </c>
       <c r="I21" s="17">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="J21" s="17">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="K21" s="18">
-        <v>12.972972972973</v>
+        <v>14.572864321608</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.686635944700</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="M21" s="18">
-        <v>28.220858895705</v>
+        <v>29.545454545454</v>
       </c>
       <c r="N21" s="18">
-        <v>-63.588850174216</v>
+        <v>-64.207221350078</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,34 +1183,34 @@
         <v>20</v>
       </c>
       <c r="D22" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E22" s="14">
         <v>-100</v>
       </c>
       <c r="F22" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G22" s="15">
         <v>9</v>
       </c>
       <c r="H22" s="14">
-        <v>-55.555555555555</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="I22" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J22" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K22" s="14">
-        <v>8.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L22" s="14">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="M22" s="14">
-        <v>116.666666666667</v>
+        <v>133.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
-        <v>2</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D23" s="15">
+        <v>1</v>
+      </c>
+      <c r="E23" s="14">
+        <v>0</v>
       </c>
       <c r="F23" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G23" s="15">
         <v>4</v>
       </c>
       <c r="H23" s="14">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I23" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J23" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K23" s="14">
-        <v>-11.111111111111</v>
+        <v>-10</v>
       </c>
       <c r="L23" s="14">
-        <v>-27.272727272727</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="M23" s="14">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D24" s="15">
         <v>13</v>
       </c>
       <c r="E24" s="14">
-        <v>46.153846153846</v>
+        <v>100</v>
       </c>
       <c r="F24" s="15">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G24" s="15">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="H24" s="14">
-        <v>26.315789473684</v>
+        <v>53.968253968254</v>
       </c>
       <c r="I24" s="15">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="J24" s="15">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="K24" s="14">
-        <v>-17.431192660550</v>
+        <v>-11.255411255411</v>
       </c>
       <c r="L24" s="14">
-        <v>-20</v>
+        <v>-19.607843137254</v>
       </c>
       <c r="M24" s="14">
-        <v>11.111111111111</v>
+        <v>20.588235294117</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D25" s="15">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E25" s="14">
-        <v>27.272727272727</v>
+        <v>128.571428571429</v>
       </c>
       <c r="F25" s="15">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G25" s="15">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="H25" s="14">
-        <v>21.818181818181</v>
+        <v>45.454545454545</v>
       </c>
       <c r="I25" s="15">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="J25" s="15">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="K25" s="14">
-        <v>-23.809523809523</v>
+        <v>-17.714285714285</v>
       </c>
       <c r="L25" s="14">
-        <v>-33.678756476683</v>
+        <v>-35.135135135135</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D26" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E26" s="14">
-        <v>66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F26" s="15">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G26" s="15">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H26" s="14">
-        <v>27.586206896551</v>
+        <v>3.125</v>
       </c>
       <c r="I26" s="15">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="J26" s="15">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="K26" s="14">
-        <v>7.017543859649</v>
+        <v>1.515151515151</v>
       </c>
       <c r="L26" s="14">
-        <v>5.172413793103</v>
+        <v>1.515151515151</v>
       </c>
       <c r="M26" s="14">
-        <v>69.444444444444</v>
+        <v>71.794871794871</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,23 +1384,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="15">
+        <v>3</v>
+      </c>
+      <c r="G27" s="15">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="15">
-        <v>4</v>
-      </c>
-      <c r="G27" s="15">
-        <v>2</v>
-      </c>
       <c r="H27" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I27" s="15">
         <v>6</v>
@@ -1426,13 +1426,13 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="15">
         <v>1</v>
       </c>
       <c r="E28" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F28" s="15">
         <v>6</v>
@@ -1444,16 +1444,16 @@
         <v>20</v>
       </c>
       <c r="I28" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J28" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K28" s="14">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="L28" s="14">
-        <v>75</v>
+        <v>36.363636363636</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1561,7 +1561,7 @@
         <v>20</v>
       </c>
       <c r="G31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="14">
         <v>-100</v>
@@ -1570,7 +1570,7 @@
         <v>20</v>
       </c>
       <c r="J31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" s="14">
         <v>-100</v>
@@ -1634,8 +1634,8 @@
       <c r="K33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L33" s="13" t="s">
-        <v>21</v>
+      <c r="L33" s="14">
+        <v>-100</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-005pct.xlsx
+++ b/data/source/weekly/cs-en-us-005pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>2</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J15" s="15">
         <v>3</v>
       </c>
       <c r="K15" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="L15" s="13" t="s">
-        <v>21</v>
+        <v>33.333333333333</v>
+      </c>
+      <c r="L15" s="14">
+        <v>300</v>
       </c>
       <c r="M15" s="14">
+        <v>300</v>
+      </c>
+      <c r="N15" s="14">
         <v>100</v>
-      </c>
-      <c r="N15" s="14">
-        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G16" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H16" s="14">
-        <v>-30</v>
+        <v>-25</v>
       </c>
       <c r="I16" s="15">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J16" s="15">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K16" s="14">
-        <v>17.391304347826</v>
+        <v>11.538461538461</v>
       </c>
       <c r="L16" s="14">
-        <v>80</v>
+        <v>70.588235294117</v>
       </c>
       <c r="M16" s="14">
-        <v>50</v>
+        <v>61.111111111111</v>
       </c>
       <c r="N16" s="14">
-        <v>-76.724137931034</v>
+        <v>-77.165354330708</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D17" s="15">
         <v>7</v>
       </c>
       <c r="E17" s="14">
-        <v>-14.285714285714</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F17" s="15">
         <v>17</v>
       </c>
       <c r="G17" s="15">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H17" s="14">
-        <v>13.333333333333</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="I17" s="15">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="J17" s="15">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K17" s="14">
-        <v>53.846153846153</v>
+        <v>45.454545454545</v>
       </c>
       <c r="L17" s="14">
-        <v>-2.439024390243</v>
+        <v>2.127659574468</v>
       </c>
       <c r="M17" s="14">
-        <v>100</v>
+        <v>108.695652173913</v>
       </c>
       <c r="N17" s="14">
-        <v>-4.761904761904</v>
+        <v>4.347826086956</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
+        <v>5</v>
+      </c>
+      <c r="D18" s="15">
+        <v>1</v>
+      </c>
+      <c r="E18" s="14">
+        <v>400</v>
+      </c>
+      <c r="F18" s="15">
+        <v>18</v>
+      </c>
+      <c r="G18" s="15">
         <v>4</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" s="15">
-        <v>19</v>
-      </c>
-      <c r="G18" s="15">
-        <v>8</v>
-      </c>
       <c r="H18" s="14">
-        <v>137.5</v>
+        <v>350</v>
       </c>
       <c r="I18" s="15">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J18" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K18" s="14">
-        <v>131.25</v>
+        <v>147.058823529412</v>
       </c>
       <c r="L18" s="14">
-        <v>2.777777777777</v>
+        <v>5</v>
       </c>
       <c r="M18" s="14">
-        <v>0</v>
+        <v>7.692307692307</v>
       </c>
       <c r="N18" s="14">
-        <v>-74.829931972789</v>
+        <v>-73.584905660377</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D19" s="15">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E19" s="14">
-        <v>60</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F19" s="15">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G19" s="15">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H19" s="14">
-        <v>-2.040816326530</v>
+        <v>0</v>
       </c>
       <c r="I19" s="15">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="J19" s="15">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="K19" s="14">
-        <v>-3.968253968253</v>
+        <v>-6.428571428571</v>
       </c>
       <c r="L19" s="14">
-        <v>-17.687074829932</v>
+        <v>-16.025641025641</v>
       </c>
       <c r="M19" s="14">
-        <v>24.742268041237</v>
+        <v>28.431372549019</v>
       </c>
       <c r="N19" s="14">
-        <v>-52.362204724409</v>
+        <v>-51.119402985074</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1110,7 +1110,7 @@
         <v>20</v>
       </c>
       <c r="G20" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H20" s="14">
         <v>-100</v>
@@ -1131,7 +1131,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N20" s="14">
-        <v>-98.666666666666</v>
+        <v>-98.701298701298</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D21" s="17">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E21" s="18">
-        <v>35.714285714285</v>
+        <v>8</v>
       </c>
       <c r="F21" s="17">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G21" s="17">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H21" s="18">
-        <v>6.976744186046</v>
+        <v>10.344827586206</v>
       </c>
       <c r="I21" s="17">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="J21" s="17">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="K21" s="18">
-        <v>14.572864321608</v>
+        <v>13.839285714285</v>
       </c>
       <c r="L21" s="18">
-        <v>-7.692307692307</v>
+        <v>-5.204460966542</v>
       </c>
       <c r="M21" s="18">
-        <v>29.545454545454</v>
+        <v>37.096774193548</v>
       </c>
       <c r="N21" s="18">
-        <v>-64.207221350078</v>
+        <v>-62.5</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="15">
+        <v>3</v>
       </c>
       <c r="D22" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="14">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="F22" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="15">
         <v>9</v>
       </c>
       <c r="H22" s="14">
-        <v>-77.777777777777</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I22" s="15">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J22" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K22" s="14">
-        <v>0</v>
+        <v>13.333333333333</v>
       </c>
       <c r="L22" s="14">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="M22" s="14">
-        <v>133.333333333333</v>
+        <v>183.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D23" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F23" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G23" s="15">
         <v>4</v>
       </c>
       <c r="H23" s="14">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I23" s="15">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J23" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K23" s="14">
-        <v>-10</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L23" s="14">
-        <v>-30.769230769230</v>
+        <v>0</v>
       </c>
       <c r="M23" s="14">
-        <v>50</v>
+        <v>85.714285714285</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D24" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E24" s="14">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F24" s="15">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="G24" s="15">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="H24" s="14">
-        <v>53.968253968254</v>
+        <v>62.962962962963</v>
       </c>
       <c r="I24" s="15">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="J24" s="15">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="K24" s="14">
-        <v>-11.255411255411</v>
+        <v>-7.818930041152</v>
       </c>
       <c r="L24" s="14">
-        <v>-19.607843137254</v>
+        <v>-19.424460431654</v>
       </c>
       <c r="M24" s="14">
-        <v>20.588235294117</v>
+        <v>24.444444444444</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D25" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E25" s="14">
-        <v>128.571428571429</v>
+        <v>62.5</v>
       </c>
       <c r="F25" s="15">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G25" s="15">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="H25" s="14">
-        <v>45.454545454545</v>
+        <v>74.285714285714</v>
       </c>
       <c r="I25" s="15">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="J25" s="15">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="K25" s="14">
-        <v>-17.714285714285</v>
+        <v>-14.207650273224</v>
       </c>
       <c r="L25" s="14">
-        <v>-35.135135135135</v>
+        <v>-34.583333333333</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D26" s="15">
         <v>9</v>
       </c>
       <c r="E26" s="14">
-        <v>-33.333333333333</v>
+        <v>22.222222222222</v>
       </c>
       <c r="F26" s="15">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G26" s="15">
         <v>32</v>
       </c>
       <c r="H26" s="14">
-        <v>3.125</v>
+        <v>-9.375</v>
       </c>
       <c r="I26" s="15">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="J26" s="15">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="K26" s="14">
-        <v>1.515151515151</v>
+        <v>1.333333333333</v>
       </c>
       <c r="L26" s="14">
-        <v>1.515151515151</v>
+        <v>-1.298701298701</v>
       </c>
       <c r="M26" s="14">
-        <v>71.794871794871</v>
+        <v>61.702127659574</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>2</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1403,16 +1403,16 @@
         <v>200</v>
       </c>
       <c r="I27" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J27" s="15">
         <v>3</v>
       </c>
       <c r="K27" s="14">
-        <v>100</v>
+        <v>166.666666666667</v>
       </c>
       <c r="L27" s="14">
-        <v>200</v>
+        <v>166.666666666667</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
-      </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>0</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G28" s="15">
         <v>5</v>
       </c>
       <c r="H28" s="14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I28" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J28" s="15">
         <v>8</v>
       </c>
       <c r="K28" s="14">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="L28" s="14">
-        <v>36.363636363636</v>
+        <v>6.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-005pct.xlsx
+++ b/data/source/weekly/cs-en-us-005pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="15">
-        <v>2</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>0</v>
       </c>
       <c r="F15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I15" s="15">
+        <v>5</v>
+      </c>
+      <c r="J15" s="15">
         <v>4</v>
       </c>
-      <c r="J15" s="15">
-        <v>3</v>
-      </c>
       <c r="K15" s="14">
-        <v>33.333333333333</v>
+        <v>25</v>
       </c>
       <c r="L15" s="14">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="M15" s="14">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="N15" s="14">
-        <v>100</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -946,28 +946,28 @@
         <v>9</v>
       </c>
       <c r="G16" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H16" s="14">
-        <v>-25</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="I16" s="15">
+        <v>31</v>
+      </c>
+      <c r="J16" s="15">
         <v>29</v>
       </c>
-      <c r="J16" s="15">
-        <v>26</v>
-      </c>
       <c r="K16" s="14">
-        <v>11.538461538461</v>
+        <v>6.896551724137</v>
       </c>
       <c r="L16" s="14">
-        <v>70.588235294117</v>
+        <v>63.157894736842</v>
       </c>
       <c r="M16" s="14">
-        <v>61.111111111111</v>
+        <v>55</v>
       </c>
       <c r="N16" s="14">
-        <v>-77.165354330708</v>
+        <v>-77.697841726618</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D17" s="15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E17" s="14">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G17" s="15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H17" s="14">
-        <v>-10.526315789473</v>
+        <v>-5</v>
       </c>
       <c r="I17" s="15">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J17" s="15">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K17" s="14">
-        <v>45.454545454545</v>
+        <v>40.540540540540</v>
       </c>
       <c r="L17" s="14">
-        <v>2.127659574468</v>
+        <v>-1.886792452830</v>
       </c>
       <c r="M17" s="14">
-        <v>108.695652173913</v>
+        <v>62.5</v>
       </c>
       <c r="N17" s="14">
-        <v>4.347826086956</v>
+        <v>-1.886792452830</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
+        <v>4</v>
+      </c>
+      <c r="D18" s="15">
         <v>5</v>
       </c>
-      <c r="D18" s="15">
-        <v>1</v>
-      </c>
       <c r="E18" s="14">
-        <v>400</v>
+        <v>-20</v>
       </c>
       <c r="F18" s="15">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G18" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H18" s="14">
-        <v>350</v>
+        <v>142.857142857143</v>
       </c>
       <c r="I18" s="15">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J18" s="15">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K18" s="14">
-        <v>147.058823529412</v>
+        <v>109.090909090909</v>
       </c>
       <c r="L18" s="14">
-        <v>5</v>
+        <v>6.976744186046</v>
       </c>
       <c r="M18" s="14">
-        <v>7.692307692307</v>
+        <v>17.948717948717</v>
       </c>
       <c r="N18" s="14">
-        <v>-73.584905660377</v>
+        <v>-74.725274725274</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D19" s="15">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E19" s="14">
-        <v>-28.571428571428</v>
+        <v>45.454545454545</v>
       </c>
       <c r="F19" s="15">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G19" s="15">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H19" s="14">
-        <v>0</v>
+        <v>2.127659574468</v>
       </c>
       <c r="I19" s="15">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="J19" s="15">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="K19" s="14">
-        <v>-6.428571428571</v>
+        <v>-2.649006622516</v>
       </c>
       <c r="L19" s="14">
-        <v>-16.025641025641</v>
+        <v>-13.017751479289</v>
       </c>
       <c r="M19" s="14">
-        <v>28.431372549019</v>
+        <v>26.724137931034</v>
       </c>
       <c r="N19" s="14">
-        <v>-51.119402985074</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1109,11 +1109,11 @@
       <c r="F20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G20" s="15">
-        <v>1</v>
-      </c>
-      <c r="H20" s="14">
-        <v>-100</v>
+      <c r="G20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I20" s="15">
         <v>1</v>
@@ -1131,7 +1131,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N20" s="14">
-        <v>-98.701298701298</v>
+        <v>-98.795180722891</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,37 +1142,37 @@
         <v>27</v>
       </c>
       <c r="D21" s="17">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="F21" s="17">
         <v>96</v>
       </c>
       <c r="G21" s="17">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H21" s="18">
-        <v>10.344827586206</v>
+        <v>7.865168539325</v>
       </c>
       <c r="I21" s="17">
-        <v>255</v>
+        <v>282</v>
       </c>
       <c r="J21" s="17">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="K21" s="18">
-        <v>13.839285714285</v>
+        <v>13.709677419354</v>
       </c>
       <c r="L21" s="18">
-        <v>-5.204460966542</v>
+        <v>-3.754266211604</v>
       </c>
       <c r="M21" s="18">
-        <v>37.096774193548</v>
+        <v>33.649289099526</v>
       </c>
       <c r="N21" s="18">
-        <v>-62.5</v>
+        <v>-62.599469496021</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" s="15">
         <v>1</v>
       </c>
       <c r="E22" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F22" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H22" s="14">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J22" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K22" s="14">
-        <v>13.333333333333</v>
+        <v>12.5</v>
       </c>
       <c r="L22" s="14">
-        <v>70</v>
+        <v>63.636363636363</v>
       </c>
       <c r="M22" s="14">
-        <v>183.333333333333</v>
+        <v>157.142857142857</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D23" s="15">
         <v>2</v>
       </c>
       <c r="E23" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F23" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G23" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H23" s="14">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="I23" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J23" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K23" s="14">
-        <v>8.333333333333</v>
+        <v>7.142857142857</v>
       </c>
       <c r="L23" s="14">
-        <v>0</v>
+        <v>15.384615384615</v>
       </c>
       <c r="M23" s="14">
-        <v>85.714285714285</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D24" s="15">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E24" s="14">
-        <v>66.666666666666</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F24" s="15">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G24" s="15">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H24" s="14">
-        <v>62.962962962963</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I24" s="15">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="J24" s="15">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="K24" s="14">
-        <v>-7.818930041152</v>
+        <v>-8.429118773946</v>
       </c>
       <c r="L24" s="14">
-        <v>-19.424460431654</v>
+        <v>-19.528619528619</v>
       </c>
       <c r="M24" s="14">
-        <v>24.444444444444</v>
+        <v>20.707070707070</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D25" s="15">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E25" s="14">
-        <v>62.5</v>
+        <v>-60</v>
       </c>
       <c r="F25" s="15">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="G25" s="15">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="H25" s="14">
-        <v>74.285714285714</v>
+        <v>19.512195121951</v>
       </c>
       <c r="I25" s="15">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="J25" s="15">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="K25" s="14">
-        <v>-14.207650273224</v>
+        <v>-17.676767676767</v>
       </c>
       <c r="L25" s="14">
-        <v>-34.583333333333</v>
+        <v>-35.573122529644</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
+        <v>7</v>
+      </c>
+      <c r="D26" s="15">
         <v>11</v>
       </c>
-      <c r="D26" s="15">
-        <v>9</v>
-      </c>
       <c r="E26" s="14">
-        <v>22.222222222222</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F26" s="15">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G26" s="15">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H26" s="14">
-        <v>-9.375</v>
+        <v>-11.428571428571</v>
       </c>
       <c r="I26" s="15">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="J26" s="15">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K26" s="14">
-        <v>1.333333333333</v>
+        <v>-4.651162790697</v>
       </c>
       <c r="L26" s="14">
-        <v>-1.298701298701</v>
+        <v>-1.204819277108</v>
       </c>
       <c r="M26" s="14">
-        <v>61.702127659574</v>
+        <v>43.859649122807</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="15">
-        <v>2</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0</v>
       </c>
       <c r="F27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="14">
+        <v>300</v>
+      </c>
+      <c r="I27" s="15">
+        <v>9</v>
+      </c>
+      <c r="J27" s="15">
+        <v>4</v>
+      </c>
+      <c r="K27" s="14">
+        <v>125</v>
+      </c>
+      <c r="L27" s="14">
         <v>200</v>
-      </c>
-      <c r="I27" s="15">
-        <v>8</v>
-      </c>
-      <c r="J27" s="15">
-        <v>3</v>
-      </c>
-      <c r="K27" s="14">
-        <v>166.666666666667</v>
-      </c>
-      <c r="L27" s="14">
-        <v>166.666666666667</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="15">
+        <v>4</v>
+      </c>
+      <c r="D28" s="15">
+        <v>2</v>
+      </c>
+      <c r="E28" s="14">
+        <v>100</v>
       </c>
       <c r="F28" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G28" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I28" s="15">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J28" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K28" s="14">
         <v>100</v>
       </c>
       <c r="L28" s="14">
-        <v>6.666666666666</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,32 +1551,32 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="15">
+        <v>4</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G31" s="15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H31" s="14">
         <v>-100</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+      <c r="I31" s="15">
+        <v>1</v>
       </c>
       <c r="J31" s="15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K31" s="14">
-        <v>-100</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="L31" s="14">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-005pct.xlsx
+++ b/data/source/weekly/cs-en-us-005pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -892,14 +892,14 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>1</v>
-      </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>0</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
         <v>3</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D16" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>-33.333333333333</v>
+        <v>400</v>
       </c>
       <c r="F16" s="15">
+        <v>10</v>
+      </c>
+      <c r="G16" s="15">
         <v>9</v>
       </c>
-      <c r="G16" s="15">
-        <v>14</v>
-      </c>
       <c r="H16" s="14">
-        <v>-35.714285714285</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I16" s="15">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="J16" s="15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K16" s="14">
-        <v>6.896551724137</v>
+        <v>20</v>
       </c>
       <c r="L16" s="14">
-        <v>63.157894736842</v>
+        <v>63.636363636363</v>
       </c>
       <c r="M16" s="14">
-        <v>55</v>
+        <v>71.428571428571</v>
       </c>
       <c r="N16" s="14">
-        <v>-77.697841726618</v>
+        <v>-76.774193548387</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" s="14">
         <v>0</v>
       </c>
       <c r="F17" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G17" s="15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H17" s="14">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="I17" s="15">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J17" s="15">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K17" s="14">
-        <v>40.540540540540</v>
+        <v>37.5</v>
       </c>
       <c r="L17" s="14">
-        <v>-1.886792452830</v>
+        <v>0</v>
       </c>
       <c r="M17" s="14">
-        <v>62.5</v>
+        <v>57.142857142857</v>
       </c>
       <c r="N17" s="14">
-        <v>-1.886792452830</v>
+        <v>-3.508771929824</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>4</v>
-      </c>
-      <c r="D18" s="15">
-        <v>5</v>
-      </c>
-      <c r="E18" s="14">
-        <v>-20</v>
+        <v>3</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="15">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G18" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H18" s="14">
-        <v>142.857142857143</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I18" s="15">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J18" s="15">
         <v>22</v>
       </c>
       <c r="K18" s="14">
-        <v>109.090909090909</v>
+        <v>122.727272727273</v>
       </c>
       <c r="L18" s="14">
-        <v>6.976744186046</v>
+        <v>11.363636363636</v>
       </c>
       <c r="M18" s="14">
-        <v>17.948717948717</v>
+        <v>22.5</v>
       </c>
       <c r="N18" s="14">
-        <v>-74.725274725274</v>
+        <v>-74.611398963730</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D19" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" s="14">
-        <v>45.454545454545</v>
+        <v>58.333333333333</v>
       </c>
       <c r="F19" s="15">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G19" s="15">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H19" s="14">
-        <v>2.127659574468</v>
+        <v>26.190476190476</v>
       </c>
       <c r="I19" s="15">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="J19" s="15">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="K19" s="14">
-        <v>-2.649006622516</v>
+        <v>1.840490797546</v>
       </c>
       <c r="L19" s="14">
-        <v>-13.017751479289</v>
+        <v>-8.791208791208</v>
       </c>
       <c r="M19" s="14">
-        <v>26.724137931034</v>
+        <v>31.746031746031</v>
       </c>
       <c r="N19" s="14">
-        <v>-50</v>
+        <v>-49.696969696969</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1125,13 +1125,13 @@
         <v>-80</v>
       </c>
       <c r="L20" s="14">
-        <v>-87.5</v>
+        <v>-88.888888888888</v>
       </c>
       <c r="M20" s="14">
         <v>-66.666666666666</v>
       </c>
       <c r="N20" s="14">
-        <v>-98.795180722891</v>
+        <v>-98.850574712643</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E21" s="18">
-        <v>12.5</v>
+        <v>87.5</v>
       </c>
       <c r="F21" s="17">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="G21" s="17">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H21" s="18">
-        <v>7.865168539325</v>
+        <v>30.379746835443</v>
       </c>
       <c r="I21" s="17">
-        <v>282</v>
+        <v>312</v>
       </c>
       <c r="J21" s="17">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="K21" s="18">
-        <v>13.709677419354</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.754266211604</v>
+        <v>-0.319488817891</v>
       </c>
       <c r="M21" s="18">
-        <v>33.649289099526</v>
+        <v>38.053097345132</v>
       </c>
       <c r="N21" s="18">
-        <v>-62.599469496021</v>
+        <v>-62.181818181818</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="15">
-        <v>1</v>
-      </c>
-      <c r="D22" s="15">
-        <v>1</v>
-      </c>
-      <c r="E22" s="14">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="15">
+        <v>7</v>
+      </c>
+      <c r="G22" s="15">
         <v>4</v>
       </c>
-      <c r="G22" s="15">
-        <v>8</v>
-      </c>
       <c r="H22" s="14">
-        <v>-50</v>
+        <v>75</v>
       </c>
       <c r="I22" s="15">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J22" s="15">
         <v>16</v>
       </c>
       <c r="K22" s="14">
-        <v>12.5</v>
+        <v>31.25</v>
       </c>
       <c r="L22" s="14">
-        <v>63.636363636363</v>
+        <v>90.909090909090</v>
       </c>
       <c r="M22" s="14">
-        <v>157.142857142857</v>
+        <v>110</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
-        <v>2</v>
-      </c>
-      <c r="D23" s="15">
-        <v>2</v>
-      </c>
-      <c r="E23" s="14">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G23" s="15">
         <v>5</v>
       </c>
       <c r="H23" s="14">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="I23" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J23" s="15">
         <v>14</v>
       </c>
       <c r="K23" s="14">
-        <v>7.142857142857</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L23" s="14">
-        <v>15.384615384615</v>
+        <v>23.076923076923</v>
       </c>
       <c r="M23" s="14">
-        <v>66.666666666666</v>
+        <v>77.777777777777</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D24" s="15">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E24" s="14">
-        <v>-11.111111111111</v>
+        <v>4.347826086956</v>
       </c>
       <c r="F24" s="15">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G24" s="15">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="H24" s="14">
-        <v>42.857142857142</v>
+        <v>27.272727272727</v>
       </c>
       <c r="I24" s="15">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="J24" s="15">
-        <v>261</v>
+        <v>284</v>
       </c>
       <c r="K24" s="14">
-        <v>-8.429118773946</v>
+        <v>-7.746478873239</v>
       </c>
       <c r="L24" s="14">
-        <v>-19.528619528619</v>
+        <v>-16.560509554140</v>
       </c>
       <c r="M24" s="14">
-        <v>20.707070707070</v>
+        <v>14.912280701754</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,13 +1303,13 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D25" s="15">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E25" s="14">
-        <v>-60</v>
+        <v>18.181818181818</v>
       </c>
       <c r="F25" s="15">
         <v>49</v>
@@ -1321,16 +1321,16 @@
         <v>19.512195121951</v>
       </c>
       <c r="I25" s="15">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="J25" s="15">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="K25" s="14">
-        <v>-17.676767676767</v>
+        <v>-15.311004784689</v>
       </c>
       <c r="L25" s="14">
-        <v>-35.573122529644</v>
+        <v>-32.954545454545</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D26" s="15">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E26" s="14">
-        <v>-36.363636363636</v>
+        <v>-62.5</v>
       </c>
       <c r="F26" s="15">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G26" s="15">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="H26" s="14">
-        <v>-11.428571428571</v>
+        <v>-40</v>
       </c>
       <c r="I26" s="15">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="J26" s="15">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="K26" s="14">
-        <v>-4.651162790697</v>
+        <v>-13.725490196078</v>
       </c>
       <c r="L26" s="14">
-        <v>-1.204819277108</v>
+        <v>-6.382978723404</v>
       </c>
       <c r="M26" s="14">
-        <v>43.859649122807</v>
+        <v>39.682539682539</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,23 +1384,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
-      </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>0</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I27" s="15">
         <v>9</v>
@@ -1412,7 +1412,7 @@
         <v>125</v>
       </c>
       <c r="L27" s="14">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D28" s="15">
         <v>2</v>
       </c>
       <c r="E28" s="14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F28" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G28" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="14">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="I28" s="15">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J28" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K28" s="14">
-        <v>100</v>
+        <v>91.666666666666</v>
       </c>
       <c r="L28" s="14">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,17 +1551,17 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
-        <v>4</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G31" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H31" s="14">
         <v>-100</v>
@@ -1576,7 +1576,7 @@
         <v>-83.333333333333</v>
       </c>
       <c r="L31" s="14">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-005pct.xlsx
+++ b/data/source/weekly/cs-en-us-005pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I15" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J15" s="15">
         <v>4</v>
       </c>
       <c r="K15" s="14">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="L15" s="14">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="M15" s="14">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="N15" s="14">
-        <v>150</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
+        <v>2</v>
+      </c>
+      <c r="D16" s="15">
         <v>5</v>
       </c>
-      <c r="D16" s="15">
-        <v>1</v>
-      </c>
       <c r="E16" s="14">
-        <v>400</v>
+        <v>-60</v>
       </c>
       <c r="F16" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G16" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H16" s="14">
-        <v>11.111111111111</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="I16" s="15">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J16" s="15">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K16" s="14">
-        <v>20</v>
+        <v>8.571428571428</v>
       </c>
       <c r="L16" s="14">
-        <v>63.636363636363</v>
+        <v>52</v>
       </c>
       <c r="M16" s="14">
-        <v>71.428571428571</v>
+        <v>72.727272727272</v>
       </c>
       <c r="N16" s="14">
-        <v>-76.774193548387</v>
+        <v>-78.651685393258</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" s="14">
         <v>0</v>
       </c>
       <c r="F17" s="15">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G17" s="15">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H17" s="14">
         <v>0</v>
       </c>
       <c r="I17" s="15">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J17" s="15">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K17" s="14">
-        <v>37.5</v>
+        <v>34.090909090909</v>
       </c>
       <c r="L17" s="14">
+        <v>1.724137931034</v>
+      </c>
+      <c r="M17" s="14">
+        <v>43.902439024390</v>
+      </c>
+      <c r="N17" s="14">
         <v>0</v>
-      </c>
-      <c r="M17" s="14">
-        <v>57.142857142857</v>
-      </c>
-      <c r="N17" s="14">
-        <v>-3.508771929824</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>3</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D18" s="15">
+        <v>2</v>
+      </c>
+      <c r="E18" s="14">
+        <v>-50</v>
       </c>
       <c r="F18" s="15">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G18" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H18" s="14">
-        <v>166.666666666667</v>
+        <v>62.5</v>
       </c>
       <c r="I18" s="15">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J18" s="15">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K18" s="14">
-        <v>122.727272727273</v>
+        <v>112.5</v>
       </c>
       <c r="L18" s="14">
-        <v>11.363636363636</v>
+        <v>10.869565217391</v>
       </c>
       <c r="M18" s="14">
-        <v>22.5</v>
+        <v>18.604651162790</v>
       </c>
       <c r="N18" s="14">
-        <v>-74.611398963730</v>
+        <v>-75.242718446601</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D19" s="15">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E19" s="14">
-        <v>58.333333333333</v>
+        <v>62.5</v>
       </c>
       <c r="F19" s="15">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G19" s="15">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H19" s="14">
-        <v>26.190476190476</v>
+        <v>24.444444444444</v>
       </c>
       <c r="I19" s="15">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="J19" s="15">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="K19" s="14">
-        <v>1.840490797546</v>
+        <v>2.923976608187</v>
       </c>
       <c r="L19" s="14">
-        <v>-8.791208791208</v>
+        <v>-7.368421052631</v>
       </c>
       <c r="M19" s="14">
-        <v>31.746031746031</v>
+        <v>35.384615384615</v>
       </c>
       <c r="N19" s="14">
-        <v>-49.696969696969</v>
+        <v>-50.974930362117</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1125,13 +1125,13 @@
         <v>-80</v>
       </c>
       <c r="L20" s="14">
-        <v>-88.888888888888</v>
+        <v>-90</v>
       </c>
       <c r="M20" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="N20" s="14">
-        <v>-98.850574712643</v>
+        <v>-98.913043478260</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>87.5</v>
+        <v>10.526315789473</v>
       </c>
       <c r="F21" s="17">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G21" s="17">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H21" s="18">
-        <v>30.379746835443</v>
+        <v>21.428571428571</v>
       </c>
       <c r="I21" s="17">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="J21" s="17">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="K21" s="18">
-        <v>18.181818181818</v>
+        <v>16.961130742049</v>
       </c>
       <c r="L21" s="18">
-        <v>-0.319488817891</v>
+        <v>0.303030303030</v>
       </c>
       <c r="M21" s="18">
-        <v>38.053097345132</v>
+        <v>37.344398340249</v>
       </c>
       <c r="N21" s="18">
-        <v>-62.181818181818</v>
+        <v>-63.140311804008</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,7 +1180,7 @@
         <v>29</v>
       </c>
       <c r="C22" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1192,10 +1192,10 @@
         <v>7</v>
       </c>
       <c r="G22" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H22" s="14">
-        <v>75</v>
+        <v>250</v>
       </c>
       <c r="I22" s="15">
         <v>21</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1230,13 +1230,13 @@
         <v>21</v>
       </c>
       <c r="F23" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G23" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H23" s="14">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="I23" s="15">
         <v>16</v>
@@ -1248,10 +1248,10 @@
         <v>14.285714285714</v>
       </c>
       <c r="L23" s="14">
-        <v>23.076923076923</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M23" s="14">
-        <v>77.777777777777</v>
+        <v>60</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D24" s="15">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E24" s="14">
-        <v>4.347826086956</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F24" s="15">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G24" s="15">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="H24" s="14">
-        <v>27.272727272727</v>
+        <v>0</v>
       </c>
       <c r="I24" s="15">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="J24" s="15">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="K24" s="14">
-        <v>-7.746478873239</v>
+        <v>-9.150326797385</v>
       </c>
       <c r="L24" s="14">
-        <v>-16.560509554140</v>
+        <v>-15.501519756838</v>
       </c>
       <c r="M24" s="14">
-        <v>14.912280701754</v>
+        <v>8.59375</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D25" s="15">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E25" s="14">
-        <v>18.181818181818</v>
+        <v>-75</v>
       </c>
       <c r="F25" s="15">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="G25" s="15">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="H25" s="14">
-        <v>19.512195121951</v>
+        <v>-29.629629629629</v>
       </c>
       <c r="I25" s="15">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="J25" s="15">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="K25" s="14">
-        <v>-15.311004784689</v>
+        <v>-20.524017467248</v>
       </c>
       <c r="L25" s="14">
-        <v>-32.954545454545</v>
+        <v>-34.057971014492</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D26" s="15">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E26" s="14">
-        <v>-62.5</v>
+        <v>0</v>
       </c>
       <c r="F26" s="15">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G26" s="15">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H26" s="14">
-        <v>-40</v>
+        <v>-30.232558139534</v>
       </c>
       <c r="I26" s="15">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="J26" s="15">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="K26" s="14">
-        <v>-13.725490196078</v>
+        <v>-13.761467889908</v>
       </c>
       <c r="L26" s="14">
-        <v>-6.382978723404</v>
+        <v>-10.476190476190</v>
       </c>
       <c r="M26" s="14">
-        <v>39.682539682539</v>
+        <v>42.424242424242</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I27" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J27" s="15">
         <v>4</v>
       </c>
       <c r="K27" s="14">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="L27" s="14">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>3</v>
       </c>
       <c r="D28" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="14">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F28" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G28" s="15">
         <v>5</v>
       </c>
       <c r="H28" s="14">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="I28" s="15">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J28" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K28" s="14">
-        <v>91.666666666666</v>
+        <v>100</v>
       </c>
       <c r="L28" s="14">
-        <v>15</v>
+        <v>23.809523809523</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1561,22 +1561,22 @@
         <v>20</v>
       </c>
       <c r="G31" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H31" s="14">
         <v>-100</v>
       </c>
-      <c r="I31" s="15">
-        <v>1</v>
+      <c r="I31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="J31" s="15">
         <v>6</v>
       </c>
       <c r="K31" s="14">
-        <v>-83.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="L31" s="14">
-        <v>-80</v>
+        <v>-100</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-005pct.xlsx
+++ b/data/source/weekly/cs-en-us-005pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I15" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J15" s="15">
         <v>4</v>
       </c>
       <c r="K15" s="14">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="L15" s="14">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="M15" s="14">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="N15" s="14">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D16" s="15">
         <v>5</v>
       </c>
       <c r="E16" s="14">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G16" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H16" s="14">
-        <v>-8.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I16" s="15">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J16" s="15">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K16" s="14">
-        <v>8.571428571428</v>
+        <v>7.5</v>
       </c>
       <c r="L16" s="14">
-        <v>52</v>
+        <v>53.571428571428</v>
       </c>
       <c r="M16" s="14">
-        <v>72.727272727272</v>
+        <v>79.166666666666</v>
       </c>
       <c r="N16" s="14">
-        <v>-78.651685393258</v>
+        <v>-78.5</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" s="15">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E17" s="14">
-        <v>0</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="F17" s="15">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G17" s="15">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H17" s="14">
-        <v>0</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I17" s="15">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="J17" s="15">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="K17" s="14">
-        <v>34.090909090909</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L17" s="14">
-        <v>1.724137931034</v>
+        <v>8.333333333333</v>
       </c>
       <c r="M17" s="14">
-        <v>43.902439024390</v>
+        <v>51.162790697674</v>
       </c>
       <c r="N17" s="14">
-        <v>0</v>
+        <v>6.557377049180</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E18" s="14">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G18" s="15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H18" s="14">
-        <v>62.5</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I18" s="15">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J18" s="15">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K18" s="14">
-        <v>112.5</v>
+        <v>85.714285714285</v>
       </c>
       <c r="L18" s="14">
-        <v>10.869565217391</v>
+        <v>1.960784313725</v>
       </c>
       <c r="M18" s="14">
-        <v>18.604651162790</v>
+        <v>10.638297872340</v>
       </c>
       <c r="N18" s="14">
-        <v>-75.242718446601</v>
+        <v>-76.146788990825</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,48 +1057,48 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D19" s="15">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E19" s="14">
-        <v>62.5</v>
+        <v>125</v>
       </c>
       <c r="F19" s="15">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G19" s="15">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="H19" s="14">
-        <v>24.444444444444</v>
+        <v>51.428571428571</v>
       </c>
       <c r="I19" s="15">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="J19" s="15">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="K19" s="14">
-        <v>2.923976608187</v>
+        <v>4.571428571428</v>
       </c>
       <c r="L19" s="14">
-        <v>-7.368421052631</v>
+        <v>-8.955223880597</v>
       </c>
       <c r="M19" s="14">
-        <v>35.384615384615</v>
+        <v>35.555555555555</v>
       </c>
       <c r="N19" s="14">
-        <v>-50.974930362117</v>
+        <v>-51.842105263157</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="15">
+        <v>2</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1106,8 +1106,8 @@
       <c r="E20" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="13" t="s">
-        <v>20</v>
+      <c r="F20" s="15">
+        <v>2</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>20</v>
@@ -1116,22 +1116,22 @@
         <v>21</v>
       </c>
       <c r="I20" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J20" s="15">
         <v>5</v>
       </c>
       <c r="K20" s="14">
-        <v>-80</v>
+        <v>-40</v>
       </c>
       <c r="L20" s="14">
-        <v>-90</v>
+        <v>-70</v>
       </c>
       <c r="M20" s="14">
-        <v>-75</v>
+        <v>-25</v>
       </c>
       <c r="N20" s="14">
-        <v>-98.913043478260</v>
+        <v>-96.875</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,45 +1142,45 @@
         <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>10.526315789473</v>
+        <v>-12.5</v>
       </c>
       <c r="F21" s="17">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="G21" s="17">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H21" s="18">
-        <v>21.428571428571</v>
+        <v>15.662650602409</v>
       </c>
       <c r="I21" s="17">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="J21" s="17">
-        <v>283</v>
+        <v>307</v>
       </c>
       <c r="K21" s="18">
-        <v>16.961130742049</v>
+        <v>14.332247557003</v>
       </c>
       <c r="L21" s="18">
-        <v>0.303030303030</v>
+        <v>0</v>
       </c>
       <c r="M21" s="18">
-        <v>37.344398340249</v>
+        <v>38.188976377952</v>
       </c>
       <c r="N21" s="18">
-        <v>-63.140311804008</v>
+        <v>-63.399374348279</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>2</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,13 +1189,13 @@
         <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G22" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" s="14">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="I22" s="15">
         <v>21</v>
@@ -1207,7 +1207,7 @@
         <v>31.25</v>
       </c>
       <c r="L22" s="14">
-        <v>90.909090909090</v>
+        <v>75</v>
       </c>
       <c r="M22" s="14">
         <v>110</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="C23" s="15">
+        <v>1</v>
+      </c>
+      <c r="D23" s="15">
+        <v>1</v>
+      </c>
+      <c r="E23" s="14">
+        <v>0</v>
       </c>
       <c r="F23" s="15">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G23" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H23" s="14">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="I23" s="15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J23" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K23" s="14">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="L23" s="14">
-        <v>14.285714285714</v>
+        <v>-6.25</v>
       </c>
       <c r="M23" s="14">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D24" s="15">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E24" s="14">
-        <v>-27.272727272727</v>
+        <v>-53.571428571428</v>
       </c>
       <c r="F24" s="15">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G24" s="15">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="H24" s="14">
-        <v>0</v>
+        <v>-24.175824175824</v>
       </c>
       <c r="I24" s="15">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="J24" s="15">
-        <v>306</v>
+        <v>334</v>
       </c>
       <c r="K24" s="14">
-        <v>-9.150326797385</v>
+        <v>-12.874251497006</v>
       </c>
       <c r="L24" s="14">
-        <v>-15.501519756838</v>
+        <v>-17.094017094017</v>
       </c>
       <c r="M24" s="14">
-        <v>8.59375</v>
+        <v>3.191489361702</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D25" s="15">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E25" s="14">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="15">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G25" s="15">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="H25" s="14">
-        <v>-29.629629629629</v>
+        <v>-46.875</v>
       </c>
       <c r="I25" s="15">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="J25" s="15">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="K25" s="14">
-        <v>-20.524017467248</v>
+        <v>-22.672064777327</v>
       </c>
       <c r="L25" s="14">
-        <v>-34.057971014492</v>
+        <v>-34.364261168384</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D26" s="15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E26" s="14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F26" s="15">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G26" s="15">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H26" s="14">
-        <v>-30.232558139534</v>
+        <v>-29.545454545454</v>
       </c>
       <c r="I26" s="15">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="J26" s="15">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="K26" s="14">
-        <v>-13.761467889908</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="L26" s="14">
-        <v>-10.476190476190</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="M26" s="14">
-        <v>42.424242424242</v>
+        <v>50</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I27" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J27" s="15">
         <v>4</v>
       </c>
       <c r="K27" s="14">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="L27" s="14">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" s="15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E28" s="14">
-        <v>200</v>
+        <v>-20</v>
       </c>
       <c r="F28" s="15">
+        <v>14</v>
+      </c>
+      <c r="G28" s="15">
         <v>10</v>
       </c>
-      <c r="G28" s="15">
-        <v>5</v>
-      </c>
       <c r="H28" s="14">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="I28" s="15">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J28" s="15">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K28" s="14">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L28" s="14">
-        <v>23.809523809523</v>
+        <v>30.434782608695</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-005pct.xlsx
+++ b/data/source/weekly/cs-en-us-005pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -895,38 +895,38 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="15">
         <v>5</v>
       </c>
       <c r="J15" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K15" s="14">
+        <v>0</v>
+      </c>
+      <c r="L15" s="14">
+        <v>150</v>
+      </c>
+      <c r="M15" s="14">
+        <v>66.666666666666</v>
+      </c>
+      <c r="N15" s="14">
         <v>25</v>
-      </c>
-      <c r="L15" s="14">
-        <v>400</v>
-      </c>
-      <c r="M15" s="14">
-        <v>400</v>
-      </c>
-      <c r="N15" s="14">
-        <v>66.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D16" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" s="14">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="15">
         <v>14</v>
       </c>
       <c r="G16" s="15">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H16" s="14">
-        <v>0</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="I16" s="15">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J16" s="15">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="K16" s="14">
-        <v>7.5</v>
+        <v>-2.173913043478</v>
       </c>
       <c r="L16" s="14">
-        <v>53.571428571428</v>
+        <v>40.625</v>
       </c>
       <c r="M16" s="14">
-        <v>79.166666666666</v>
+        <v>73.076923076923</v>
       </c>
       <c r="N16" s="14">
-        <v>-78.5</v>
+        <v>-78.260869565217</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D17" s="15">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E17" s="14">
-        <v>-54.545454545454</v>
+        <v>600</v>
       </c>
       <c r="F17" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G17" s="15">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H17" s="14">
-        <v>-27.272727272727</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="I17" s="15">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J17" s="15">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K17" s="14">
-        <v>18.181818181818</v>
+        <v>26.785714285714</v>
       </c>
       <c r="L17" s="14">
-        <v>8.333333333333</v>
+        <v>16.393442622950</v>
       </c>
       <c r="M17" s="14">
-        <v>51.162790697674</v>
+        <v>47.916666666666</v>
       </c>
       <c r="N17" s="14">
-        <v>6.557377049180</v>
+        <v>2.898550724637</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="15">
+        <v>6</v>
       </c>
       <c r="D18" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E18" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G18" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H18" s="14">
-        <v>-18.181818181818</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="I18" s="15">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J18" s="15">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="K18" s="14">
-        <v>85.714285714285</v>
+        <v>70.588235294117</v>
       </c>
       <c r="L18" s="14">
-        <v>1.960784313725</v>
+        <v>9.433962264150</v>
       </c>
       <c r="M18" s="14">
-        <v>10.638297872340</v>
+        <v>20.833333333333</v>
       </c>
       <c r="N18" s="14">
-        <v>-76.146788990825</v>
+        <v>-74.222222222222</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,48 +1057,48 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D19" s="15">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E19" s="14">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="F19" s="15">
         <v>53</v>
       </c>
       <c r="G19" s="15">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H19" s="14">
-        <v>51.428571428571</v>
+        <v>35.897435897435</v>
       </c>
       <c r="I19" s="15">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="J19" s="15">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="K19" s="14">
-        <v>4.571428571428</v>
+        <v>4.210526315789</v>
       </c>
       <c r="L19" s="14">
-        <v>-8.955223880597</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="M19" s="14">
-        <v>35.555555555555</v>
+        <v>34.693877551020</v>
       </c>
       <c r="N19" s="14">
-        <v>-51.842105263157</v>
+        <v>-51.941747572815</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>2</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1131,7 +1131,7 @@
         <v>-25</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.875</v>
+        <v>-97.142857142857</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,54 +1139,54 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18">
-        <v>-12.5</v>
+        <v>3.448275862068</v>
       </c>
       <c r="F21" s="17">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G21" s="17">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="H21" s="18">
-        <v>15.662650602409</v>
+        <v>12.5</v>
       </c>
       <c r="I21" s="17">
-        <v>351</v>
+        <v>380</v>
       </c>
       <c r="J21" s="17">
-        <v>307</v>
+        <v>336</v>
       </c>
       <c r="K21" s="18">
-        <v>14.332247557003</v>
+        <v>13.095238095238</v>
       </c>
       <c r="L21" s="18">
-        <v>0</v>
+        <v>3.542234332425</v>
       </c>
       <c r="M21" s="18">
-        <v>38.188976377952</v>
+        <v>37.681159420289</v>
       </c>
       <c r="N21" s="18">
-        <v>-63.399374348279</v>
+        <v>-62.854349951124</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="15">
+        <v>1</v>
+      </c>
+      <c r="D22" s="15">
+        <v>1</v>
+      </c>
+      <c r="E22" s="14">
+        <v>0</v>
       </c>
       <c r="F22" s="15">
         <v>4</v>
@@ -1198,19 +1198,19 @@
         <v>300</v>
       </c>
       <c r="I22" s="15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J22" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K22" s="14">
-        <v>31.25</v>
+        <v>29.411764705882</v>
       </c>
       <c r="L22" s="14">
-        <v>75</v>
+        <v>57.142857142857</v>
       </c>
       <c r="M22" s="14">
-        <v>110</v>
+        <v>83.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="15">
         <v>1</v>
       </c>
       <c r="E23" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G23" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I23" s="15">
         <v>15</v>
       </c>
       <c r="J23" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K23" s="14">
-        <v>0</v>
+        <v>-6.25</v>
       </c>
       <c r="L23" s="14">
         <v>-6.25</v>
       </c>
       <c r="M23" s="14">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D24" s="15">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E24" s="14">
-        <v>-53.571428571428</v>
+        <v>25</v>
       </c>
       <c r="F24" s="15">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G24" s="15">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H24" s="14">
-        <v>-24.175824175824</v>
+        <v>-16.129032258064</v>
       </c>
       <c r="I24" s="15">
-        <v>291</v>
+        <v>316</v>
       </c>
       <c r="J24" s="15">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="K24" s="14">
-        <v>-12.874251497006</v>
+        <v>-10.734463276836</v>
       </c>
       <c r="L24" s="14">
-        <v>-17.094017094017</v>
+        <v>-14.130434782608</v>
       </c>
       <c r="M24" s="14">
-        <v>3.191489361702</v>
+        <v>1.607717041800</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D25" s="15">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E25" s="14">
-        <v>-50</v>
+        <v>13.333333333333</v>
       </c>
       <c r="F25" s="15">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G25" s="15">
         <v>64</v>
       </c>
       <c r="H25" s="14">
-        <v>-46.875</v>
+        <v>-31.25</v>
       </c>
       <c r="I25" s="15">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="J25" s="15">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="K25" s="14">
-        <v>-22.672064777327</v>
+        <v>-20.610687022900</v>
       </c>
       <c r="L25" s="14">
-        <v>-34.364261168384</v>
+        <v>-31.803278688524</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D26" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E26" s="14">
-        <v>20</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F26" s="15">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G26" s="15">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H26" s="14">
-        <v>-29.545454545454</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="I26" s="15">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="J26" s="15">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="K26" s="14">
-        <v>-11.764705882352</v>
+        <v>-11.71875</v>
       </c>
       <c r="L26" s="14">
-        <v>-8.695652173913</v>
+        <v>-8.870967741935</v>
       </c>
       <c r="M26" s="14">
-        <v>50</v>
+        <v>46.753246753246</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,14 +1384,14 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="15">
+        <v>1</v>
+      </c>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0</v>
       </c>
       <c r="F27" s="15">
         <v>2</v>
@@ -1403,16 +1403,16 @@
         <v>100</v>
       </c>
       <c r="I27" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J27" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K27" s="14">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="L27" s="14">
-        <v>80</v>
+        <v>42.857142857142</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D28" s="15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E28" s="14">
-        <v>-20</v>
+        <v>100</v>
       </c>
       <c r="F28" s="15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G28" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H28" s="14">
-        <v>40</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I28" s="15">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J28" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K28" s="14">
-        <v>66.666666666666</v>
+        <v>68.421052631578</v>
       </c>
       <c r="L28" s="14">
-        <v>30.434782608695</v>
+        <v>39.130434782608</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1560,11 +1560,11 @@
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="15">
-        <v>4</v>
-      </c>
-      <c r="H31" s="14">
-        <v>-100</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-005pct.xlsx
+++ b/data/source/weekly/cs-en-us-005pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -329,8 +329,8 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#0"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;&quot;-&quot;#,##0.00"/>
   </numFmts>
   <fonts count="12">
@@ -546,7 +546,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -564,7 +564,7 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -854,29 +854,29 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>21</v>
+      <c r="J14" s="14">
+        <v>1</v>
+      </c>
+      <c r="K14" s="15">
+        <v>-100</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>21</v>
@@ -884,7 +884,7 @@
       <c r="M14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N14" s="14">
+      <c r="N14" s="15">
         <v>-100</v>
       </c>
     </row>
@@ -895,37 +895,37 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="15">
         <v>-100</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="14">
         <v>1</v>
       </c>
-      <c r="G15" s="15">
-        <v>1</v>
-      </c>
-      <c r="H15" s="14">
-        <v>0</v>
-      </c>
-      <c r="I15" s="15">
+      <c r="G15" s="14">
+        <v>2</v>
+      </c>
+      <c r="H15" s="15">
+        <v>-50</v>
+      </c>
+      <c r="I15" s="14">
         <v>5</v>
       </c>
-      <c r="J15" s="15">
-        <v>5</v>
-      </c>
-      <c r="K15" s="14">
-        <v>0</v>
-      </c>
-      <c r="L15" s="14">
+      <c r="J15" s="14">
+        <v>6</v>
+      </c>
+      <c r="K15" s="15">
+        <v>-16.666666666666</v>
+      </c>
+      <c r="L15" s="15">
         <v>150</v>
       </c>
-      <c r="M15" s="14">
+      <c r="M15" s="15">
         <v>66.666666666666</v>
       </c>
-      <c r="N15" s="14">
+      <c r="N15" s="15">
         <v>25</v>
       </c>
     </row>
@@ -933,164 +933,164 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>2</v>
-      </c>
-      <c r="D16" s="15">
-        <v>6</v>
-      </c>
-      <c r="E16" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="F16" s="15">
-        <v>14</v>
-      </c>
-      <c r="G16" s="15">
-        <v>17</v>
-      </c>
-      <c r="H16" s="14">
-        <v>-17.647058823529</v>
-      </c>
-      <c r="I16" s="15">
-        <v>45</v>
-      </c>
-      <c r="J16" s="15">
-        <v>46</v>
-      </c>
-      <c r="K16" s="14">
-        <v>-2.173913043478</v>
-      </c>
-      <c r="L16" s="14">
-        <v>40.625</v>
-      </c>
-      <c r="M16" s="14">
-        <v>73.076923076923</v>
-      </c>
-      <c r="N16" s="14">
-        <v>-78.260869565217</v>
+      <c r="C16" s="14">
+        <v>4</v>
+      </c>
+      <c r="D16" s="14">
+        <v>4</v>
+      </c>
+      <c r="E16" s="15">
+        <v>0</v>
+      </c>
+      <c r="F16" s="14">
+        <v>13</v>
+      </c>
+      <c r="G16" s="14">
+        <v>20</v>
+      </c>
+      <c r="H16" s="15">
+        <v>-35</v>
+      </c>
+      <c r="I16" s="14">
+        <v>49</v>
+      </c>
+      <c r="J16" s="14">
+        <v>50</v>
+      </c>
+      <c r="K16" s="15">
+        <v>-2</v>
+      </c>
+      <c r="L16" s="15">
+        <v>44.117647058823</v>
+      </c>
+      <c r="M16" s="15">
+        <v>81.481481481481</v>
+      </c>
+      <c r="N16" s="15">
+        <v>-77.522935779816</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="14">
         <v>7</v>
       </c>
-      <c r="D17" s="15">
-        <v>1</v>
-      </c>
-      <c r="E17" s="14">
-        <v>600</v>
-      </c>
-      <c r="F17" s="15">
-        <v>18</v>
-      </c>
-      <c r="G17" s="15">
-        <v>19</v>
-      </c>
-      <c r="H17" s="14">
-        <v>-5.263157894736</v>
-      </c>
-      <c r="I17" s="15">
-        <v>71</v>
-      </c>
-      <c r="J17" s="15">
-        <v>56</v>
-      </c>
-      <c r="K17" s="14">
-        <v>26.785714285714</v>
-      </c>
-      <c r="L17" s="14">
-        <v>16.393442622950</v>
-      </c>
-      <c r="M17" s="14">
-        <v>47.916666666666</v>
-      </c>
-      <c r="N17" s="14">
-        <v>2.898550724637</v>
+      <c r="D17" s="14">
+        <v>5</v>
+      </c>
+      <c r="E17" s="15">
+        <v>40</v>
+      </c>
+      <c r="F17" s="14">
+        <v>22</v>
+      </c>
+      <c r="G17" s="14">
+        <v>21</v>
+      </c>
+      <c r="H17" s="15">
+        <v>4.761904761904</v>
+      </c>
+      <c r="I17" s="14">
+        <v>78</v>
+      </c>
+      <c r="J17" s="14">
+        <v>61</v>
+      </c>
+      <c r="K17" s="15">
+        <v>27.868852459016</v>
+      </c>
+      <c r="L17" s="15">
+        <v>20</v>
+      </c>
+      <c r="M17" s="15">
+        <v>59.183673469387</v>
+      </c>
+      <c r="N17" s="15">
+        <v>6.849315068493</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>6</v>
-      </c>
-      <c r="D18" s="15">
-        <v>6</v>
-      </c>
-      <c r="E18" s="14">
+      <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15">
         <v>0</v>
       </c>
-      <c r="F18" s="15">
-        <v>11</v>
-      </c>
-      <c r="G18" s="15">
-        <v>12</v>
-      </c>
-      <c r="H18" s="14">
-        <v>-8.333333333333</v>
-      </c>
-      <c r="I18" s="15">
-        <v>58</v>
-      </c>
-      <c r="J18" s="15">
-        <v>34</v>
-      </c>
-      <c r="K18" s="14">
-        <v>70.588235294117</v>
-      </c>
-      <c r="L18" s="14">
-        <v>9.433962264150</v>
-      </c>
-      <c r="M18" s="14">
-        <v>20.833333333333</v>
-      </c>
-      <c r="N18" s="14">
-        <v>-74.222222222222</v>
+      <c r="F18" s="14">
+        <v>9</v>
+      </c>
+      <c r="G18" s="14">
+        <v>13</v>
+      </c>
+      <c r="H18" s="15">
+        <v>-30.769230769230</v>
+      </c>
+      <c r="I18" s="14">
+        <v>59</v>
+      </c>
+      <c r="J18" s="14">
+        <v>35</v>
+      </c>
+      <c r="K18" s="15">
+        <v>68.571428571428</v>
+      </c>
+      <c r="L18" s="15">
+        <v>5.357142857142</v>
+      </c>
+      <c r="M18" s="15">
+        <v>22.916666666666</v>
+      </c>
+      <c r="N18" s="15">
+        <v>-76.209677419354</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="15">
-        <v>15</v>
-      </c>
-      <c r="D19" s="15">
-        <v>15</v>
-      </c>
-      <c r="E19" s="14">
-        <v>0</v>
-      </c>
-      <c r="F19" s="15">
-        <v>53</v>
-      </c>
-      <c r="G19" s="15">
+      <c r="C19" s="14">
+        <v>14</v>
+      </c>
+      <c r="D19" s="14">
+        <v>12</v>
+      </c>
+      <c r="E19" s="15">
+        <v>16.666666666666</v>
+      </c>
+      <c r="F19" s="14">
+        <v>49</v>
+      </c>
+      <c r="G19" s="14">
         <v>39</v>
       </c>
-      <c r="H19" s="14">
-        <v>35.897435897435</v>
-      </c>
-      <c r="I19" s="15">
-        <v>198</v>
-      </c>
-      <c r="J19" s="15">
-        <v>190</v>
-      </c>
-      <c r="K19" s="14">
-        <v>4.210526315789</v>
-      </c>
-      <c r="L19" s="14">
-        <v>-5.263157894736</v>
-      </c>
-      <c r="M19" s="14">
-        <v>34.693877551020</v>
-      </c>
-      <c r="N19" s="14">
-        <v>-51.941747572815</v>
+      <c r="H19" s="15">
+        <v>25.641025641025</v>
+      </c>
+      <c r="I19" s="14">
+        <v>211</v>
+      </c>
+      <c r="J19" s="14">
+        <v>202</v>
+      </c>
+      <c r="K19" s="15">
+        <v>4.455445544554</v>
+      </c>
+      <c r="L19" s="15">
+        <v>-5.803571428571</v>
+      </c>
+      <c r="M19" s="15">
+        <v>31.875</v>
+      </c>
+      <c r="N19" s="15">
+        <v>-53.111111111111</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1106,7 +1106,7 @@
       <c r="E20" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="15">
+      <c r="F20" s="14">
         <v>2</v>
       </c>
       <c r="G20" s="13" t="s">
@@ -1115,23 +1115,23 @@
       <c r="H20" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I20" s="15">
+      <c r="I20" s="14">
         <v>3</v>
       </c>
-      <c r="J20" s="15">
+      <c r="J20" s="14">
         <v>5</v>
       </c>
-      <c r="K20" s="14">
+      <c r="K20" s="15">
         <v>-40</v>
       </c>
-      <c r="L20" s="14">
+      <c r="L20" s="15">
         <v>-70</v>
       </c>
-      <c r="M20" s="14">
+      <c r="M20" s="15">
         <v>-25</v>
       </c>
-      <c r="N20" s="14">
-        <v>-97.142857142857</v>
+      <c r="N20" s="15">
+        <v>-97.272727272727</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D21" s="17">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>3.448275862068</v>
+        <v>8.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G21" s="17">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H21" s="18">
+        <v>0</v>
+      </c>
+      <c r="I21" s="17">
+        <v>405</v>
+      </c>
+      <c r="J21" s="17">
+        <v>360</v>
+      </c>
+      <c r="K21" s="18">
         <v>12.5</v>
       </c>
-      <c r="I21" s="17">
-        <v>380</v>
-      </c>
-      <c r="J21" s="17">
-        <v>336</v>
-      </c>
-      <c r="K21" s="18">
-        <v>13.095238095238</v>
-      </c>
       <c r="L21" s="18">
-        <v>3.542234332425</v>
+        <v>3.580562659846</v>
       </c>
       <c r="M21" s="18">
-        <v>37.681159420289</v>
+        <v>39.175257731958</v>
       </c>
       <c r="N21" s="18">
-        <v>-62.854349951124</v>
+        <v>-63.348416289592</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="14">
+        <v>4</v>
+      </c>
+      <c r="D22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="15">
-        <v>1</v>
-      </c>
-      <c r="E22" s="14">
-        <v>0</v>
-      </c>
-      <c r="F22" s="15">
-        <v>4</v>
-      </c>
-      <c r="G22" s="15">
-        <v>1</v>
-      </c>
-      <c r="H22" s="14">
+      <c r="E22" s="15">
         <v>300</v>
       </c>
-      <c r="I22" s="15">
-        <v>22</v>
-      </c>
-      <c r="J22" s="15">
-        <v>17</v>
-      </c>
-      <c r="K22" s="14">
-        <v>29.411764705882</v>
-      </c>
-      <c r="L22" s="14">
-        <v>57.142857142857</v>
-      </c>
-      <c r="M22" s="14">
-        <v>83.333333333333</v>
+      <c r="F22" s="14">
+        <v>7</v>
+      </c>
+      <c r="G22" s="14">
+        <v>2</v>
+      </c>
+      <c r="H22" s="15">
+        <v>250</v>
+      </c>
+      <c r="I22" s="14">
+        <v>26</v>
+      </c>
+      <c r="J22" s="14">
+        <v>18</v>
+      </c>
+      <c r="K22" s="15">
+        <v>44.444444444444</v>
+      </c>
+      <c r="L22" s="15">
+        <v>85.714285714285</v>
+      </c>
+      <c r="M22" s="15">
+        <v>116.666666666667</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="15">
+      <c r="C23" s="14">
         <v>1</v>
       </c>
-      <c r="E23" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F23" s="15">
-        <v>1</v>
-      </c>
-      <c r="G23" s="15">
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="14">
         <v>2</v>
       </c>
-      <c r="H23" s="14">
-        <v>-50</v>
-      </c>
-      <c r="I23" s="15">
-        <v>15</v>
-      </c>
-      <c r="J23" s="15">
+      <c r="G23" s="14">
+        <v>2</v>
+      </c>
+      <c r="H23" s="15">
+        <v>0</v>
+      </c>
+      <c r="I23" s="14">
         <v>16</v>
       </c>
-      <c r="K23" s="14">
-        <v>-6.25</v>
-      </c>
-      <c r="L23" s="14">
-        <v>-6.25</v>
-      </c>
-      <c r="M23" s="14">
-        <v>25</v>
+      <c r="J23" s="14">
+        <v>16</v>
+      </c>
+      <c r="K23" s="15">
+        <v>0</v>
+      </c>
+      <c r="L23" s="15">
+        <v>-5.882352941176</v>
+      </c>
+      <c r="M23" s="15">
+        <v>33.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1261,38 +1261,38 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="15">
-        <v>25</v>
-      </c>
-      <c r="D24" s="15">
-        <v>20</v>
-      </c>
-      <c r="E24" s="14">
-        <v>25</v>
-      </c>
-      <c r="F24" s="15">
-        <v>78</v>
-      </c>
-      <c r="G24" s="15">
-        <v>93</v>
-      </c>
-      <c r="H24" s="14">
-        <v>-16.129032258064</v>
-      </c>
-      <c r="I24" s="15">
-        <v>316</v>
-      </c>
-      <c r="J24" s="15">
-        <v>354</v>
-      </c>
-      <c r="K24" s="14">
-        <v>-10.734463276836</v>
-      </c>
-      <c r="L24" s="14">
-        <v>-14.130434782608</v>
-      </c>
-      <c r="M24" s="14">
-        <v>1.607717041800</v>
+      <c r="C24" s="14">
+        <v>19</v>
+      </c>
+      <c r="D24" s="14">
+        <v>16</v>
+      </c>
+      <c r="E24" s="15">
+        <v>18.75</v>
+      </c>
+      <c r="F24" s="14">
+        <v>72</v>
+      </c>
+      <c r="G24" s="14">
+        <v>86</v>
+      </c>
+      <c r="H24" s="15">
+        <v>-16.279069767441</v>
+      </c>
+      <c r="I24" s="14">
+        <v>334</v>
+      </c>
+      <c r="J24" s="14">
+        <v>370</v>
+      </c>
+      <c r="K24" s="15">
+        <v>-9.729729729729</v>
+      </c>
+      <c r="L24" s="15">
+        <v>-12.565445026178</v>
+      </c>
+      <c r="M24" s="15">
+        <v>0.300300300300</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="14">
+        <v>11</v>
+      </c>
+      <c r="D25" s="14">
         <v>17</v>
       </c>
-      <c r="D25" s="15">
-        <v>15</v>
-      </c>
-      <c r="E25" s="14">
-        <v>13.333333333333</v>
-      </c>
-      <c r="F25" s="15">
-        <v>44</v>
-      </c>
-      <c r="G25" s="15">
-        <v>64</v>
-      </c>
-      <c r="H25" s="14">
-        <v>-31.25</v>
-      </c>
-      <c r="I25" s="15">
-        <v>208</v>
-      </c>
-      <c r="J25" s="15">
-        <v>262</v>
-      </c>
-      <c r="K25" s="14">
-        <v>-20.610687022900</v>
-      </c>
-      <c r="L25" s="14">
-        <v>-31.803278688524</v>
+      <c r="E25" s="15">
+        <v>-35.294117647058</v>
+      </c>
+      <c r="F25" s="14">
+        <v>41</v>
+      </c>
+      <c r="G25" s="14">
+        <v>70</v>
+      </c>
+      <c r="H25" s="15">
+        <v>-41.428571428571</v>
+      </c>
+      <c r="I25" s="14">
+        <v>218</v>
+      </c>
+      <c r="J25" s="14">
+        <v>279</v>
+      </c>
+      <c r="K25" s="15">
+        <v>-21.863799283154</v>
+      </c>
+      <c r="L25" s="15">
+        <v>-30.351437699680</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1343,38 +1343,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="15">
-        <v>7</v>
-      </c>
-      <c r="D26" s="15">
-        <v>9</v>
-      </c>
-      <c r="E26" s="14">
-        <v>-22.222222222222</v>
-      </c>
-      <c r="F26" s="15">
-        <v>32</v>
-      </c>
-      <c r="G26" s="15">
-        <v>42</v>
-      </c>
-      <c r="H26" s="14">
-        <v>-23.809523809523</v>
-      </c>
-      <c r="I26" s="15">
-        <v>113</v>
-      </c>
-      <c r="J26" s="15">
-        <v>128</v>
-      </c>
-      <c r="K26" s="14">
-        <v>-11.71875</v>
-      </c>
-      <c r="L26" s="14">
-        <v>-8.870967741935</v>
-      </c>
-      <c r="M26" s="14">
-        <v>46.753246753246</v>
+      <c r="C26" s="14">
+        <v>6</v>
+      </c>
+      <c r="D26" s="14">
+        <v>11</v>
+      </c>
+      <c r="E26" s="15">
+        <v>-45.454545454545</v>
+      </c>
+      <c r="F26" s="14">
+        <v>34</v>
+      </c>
+      <c r="G26" s="14">
+        <v>37</v>
+      </c>
+      <c r="H26" s="15">
+        <v>-8.108108108108</v>
+      </c>
+      <c r="I26" s="14">
+        <v>120</v>
+      </c>
+      <c r="J26" s="14">
+        <v>139</v>
+      </c>
+      <c r="K26" s="15">
+        <v>-13.669064748201</v>
+      </c>
+      <c r="L26" s="15">
+        <v>-10.447761194029</v>
+      </c>
+      <c r="M26" s="15">
+        <v>50</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
+      <c r="E27" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F27" s="14">
+        <v>2</v>
+      </c>
+      <c r="G27" s="14">
+        <v>2</v>
+      </c>
+      <c r="H27" s="15">
         <v>0</v>
       </c>
-      <c r="F27" s="15">
-        <v>2</v>
-      </c>
-      <c r="G27" s="15">
-        <v>1</v>
-      </c>
-      <c r="H27" s="14">
-        <v>100</v>
-      </c>
-      <c r="I27" s="15">
+      <c r="I27" s="14">
         <v>10</v>
       </c>
-      <c r="J27" s="15">
-        <v>5</v>
-      </c>
-      <c r="K27" s="14">
-        <v>100</v>
-      </c>
-      <c r="L27" s="14">
-        <v>42.857142857142</v>
+      <c r="J27" s="14">
+        <v>6</v>
+      </c>
+      <c r="K27" s="15">
+        <v>66.666666666666</v>
+      </c>
+      <c r="L27" s="15">
+        <v>25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E28" s="15">
         <v>100</v>
       </c>
-      <c r="F28" s="15">
-        <v>12</v>
-      </c>
-      <c r="G28" s="15">
-        <v>9</v>
-      </c>
-      <c r="H28" s="14">
-        <v>33.333333333333</v>
-      </c>
-      <c r="I28" s="15">
-        <v>32</v>
-      </c>
-      <c r="J28" s="15">
-        <v>19</v>
-      </c>
-      <c r="K28" s="14">
-        <v>68.421052631578</v>
-      </c>
-      <c r="L28" s="14">
-        <v>39.130434782608</v>
+      <c r="F28" s="14">
+        <v>11</v>
+      </c>
+      <c r="G28" s="14">
+        <v>8</v>
+      </c>
+      <c r="H28" s="15">
+        <v>37.5</v>
+      </c>
+      <c r="I28" s="14">
+        <v>34</v>
+      </c>
+      <c r="J28" s="14">
+        <v>20</v>
+      </c>
+      <c r="K28" s="15">
+        <v>70</v>
+      </c>
+      <c r="L28" s="15">
+        <v>36</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1499,7 +1499,7 @@
       <c r="M29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N29" s="14">
+      <c r="N29" s="15">
         <v>-100</v>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       <c r="M30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N30" s="14">
+      <c r="N30" s="15">
         <v>-100</v>
       </c>
     </row>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1566,17 +1566,17 @@
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J31" s="15">
+      <c r="I31" s="14">
+        <v>1</v>
+      </c>
+      <c r="J31" s="14">
         <v>6</v>
       </c>
-      <c r="K31" s="14">
-        <v>-100</v>
-      </c>
-      <c r="L31" s="14">
-        <v>-100</v>
+      <c r="K31" s="15">
+        <v>-83.333333333333</v>
+      </c>
+      <c r="L31" s="15">
+        <v>-88.888888888888</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1634,7 +1634,7 @@
       <c r="K33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L33" s="14">
+      <c r="L33" s="15">
         <v>-100</v>
       </c>
       <c r="M33" s="13" t="s">
@@ -1742,31 +1742,31 @@
       <c r="A39" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="14">
         <v>19</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="14">
         <v>10</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="14">
         <v>3</v>
       </c>
-      <c r="I39" s="15">
+      <c r="I39" s="14">
         <v>3</v>
       </c>
-      <c r="J39" s="15">
+      <c r="J39" s="14">
         <v>4</v>
       </c>
-      <c r="K39" s="14">
+      <c r="K39" s="15">
         <v>33.333333333333</v>
       </c>
-      <c r="L39" s="14">
+      <c r="L39" s="15">
         <v>33.333333333333</v>
       </c>
-      <c r="M39" s="14">
+      <c r="M39" s="15">
         <v>-60</v>
       </c>
-      <c r="N39" s="14">
+      <c r="N39" s="15">
         <v>-78.947368421052</v>
       </c>
     </row>
@@ -1774,31 +1774,31 @@
       <c r="A40" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="14">
         <v>10</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="14">
         <v>12</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="14">
         <v>6</v>
       </c>
-      <c r="I40" s="15">
+      <c r="I40" s="14">
         <v>3</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="14">
         <v>25</v>
       </c>
-      <c r="K40" s="14">
+      <c r="K40" s="15">
         <v>733.333333333333</v>
       </c>
-      <c r="L40" s="14">
+      <c r="L40" s="15">
         <v>316.666666666667</v>
       </c>
-      <c r="M40" s="14">
+      <c r="M40" s="15">
         <v>108.333333333333</v>
       </c>
-      <c r="N40" s="14">
+      <c r="N40" s="15">
         <v>150</v>
       </c>
     </row>
@@ -1806,31 +1806,31 @@
       <c r="A41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="14">
         <v>983</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="14">
         <v>827</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="14">
         <v>319</v>
       </c>
-      <c r="I41" s="15">
+      <c r="I41" s="14">
         <v>250</v>
       </c>
-      <c r="J41" s="15">
+      <c r="J41" s="14">
         <v>150</v>
       </c>
-      <c r="K41" s="14">
+      <c r="K41" s="15">
         <v>-40</v>
       </c>
-      <c r="L41" s="14">
+      <c r="L41" s="15">
         <v>-52.978056426332</v>
       </c>
-      <c r="M41" s="14">
+      <c r="M41" s="15">
         <v>-81.862152357920</v>
       </c>
-      <c r="N41" s="14">
+      <c r="N41" s="15">
         <v>-84.740590030518</v>
       </c>
     </row>
@@ -1838,31 +1838,31 @@
       <c r="A42" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="14">
         <v>251</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="14">
         <v>303</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="14">
         <v>239</v>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="14">
         <v>136</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="14">
         <v>301</v>
       </c>
-      <c r="K42" s="14">
+      <c r="K42" s="15">
         <v>121.323529411765</v>
       </c>
-      <c r="L42" s="14">
+      <c r="L42" s="15">
         <v>25.941422594142</v>
       </c>
-      <c r="M42" s="14">
+      <c r="M42" s="15">
         <v>-0.660066006600</v>
       </c>
-      <c r="N42" s="14">
+      <c r="N42" s="15">
         <v>19.920318725099</v>
       </c>
     </row>
@@ -1870,31 +1870,31 @@
       <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="14">
         <v>863</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="14">
         <v>787</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="14">
         <v>331</v>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="14">
         <v>236</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="14">
         <v>132</v>
       </c>
-      <c r="K43" s="14">
+      <c r="K43" s="15">
         <v>-44.067796610169</v>
       </c>
-      <c r="L43" s="14">
+      <c r="L43" s="15">
         <v>-60.120845921450</v>
       </c>
-      <c r="M43" s="14">
+      <c r="M43" s="15">
         <v>-83.227445997458</v>
       </c>
-      <c r="N43" s="14">
+      <c r="N43" s="15">
         <v>-84.704519119351</v>
       </c>
     </row>
@@ -1902,31 +1902,31 @@
       <c r="A44" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="14">
         <v>1829</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="14">
         <v>1587</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="14">
         <v>919</v>
       </c>
-      <c r="I44" s="15">
+      <c r="I44" s="14">
         <v>657</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="14">
         <v>722</v>
       </c>
-      <c r="K44" s="14">
+      <c r="K44" s="15">
         <v>9.893455098934</v>
       </c>
-      <c r="L44" s="14">
+      <c r="L44" s="15">
         <v>-21.436343852013</v>
       </c>
-      <c r="M44" s="14">
+      <c r="M44" s="15">
         <v>-54.505356017643</v>
       </c>
-      <c r="N44" s="14">
+      <c r="N44" s="15">
         <v>-60.524876981957</v>
       </c>
     </row>
@@ -1934,31 +1934,31 @@
       <c r="A45" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="14">
         <v>521</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="14">
         <v>337</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="14">
         <v>148</v>
       </c>
-      <c r="I45" s="15">
+      <c r="I45" s="14">
         <v>97</v>
       </c>
-      <c r="J45" s="15">
-        <v>21</v>
-      </c>
-      <c r="K45" s="14">
+      <c r="J45" s="14">
+        <v>21</v>
+      </c>
+      <c r="K45" s="15">
         <v>-78.350515463917</v>
       </c>
-      <c r="L45" s="14">
+      <c r="L45" s="15">
         <v>-85.810810810810</v>
       </c>
-      <c r="M45" s="14">
+      <c r="M45" s="15">
         <v>-93.768545994065</v>
       </c>
-      <c r="N45" s="14">
+      <c r="N45" s="15">
         <v>-95.969289827255</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-005pct.xlsx
+++ b/data/source/weekly/cs-en-us-005pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>-16.666666666666</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L15" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="M15" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="N15" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
         <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
         <v>13</v>
       </c>
       <c r="G16" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H16" s="15">
-        <v>-35</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="I16" s="14">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J16" s="14">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K16" s="15">
-        <v>-2</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="L16" s="15">
-        <v>44.117647058823</v>
+        <v>45.714285714285</v>
       </c>
       <c r="M16" s="15">
-        <v>81.481481481481</v>
+        <v>82.142857142857</v>
       </c>
       <c r="N16" s="15">
-        <v>-77.522935779816</v>
+        <v>-77.631578947368</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E17" s="15">
-        <v>40</v>
+        <v>-20</v>
       </c>
       <c r="F17" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G17" s="14">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H17" s="15">
-        <v>4.761904761904</v>
+        <v>-3.703703703703</v>
       </c>
       <c r="I17" s="14">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="J17" s="14">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="K17" s="15">
-        <v>27.868852459016</v>
+        <v>21.126760563380</v>
       </c>
       <c r="L17" s="15">
-        <v>20</v>
+        <v>26.470588235294</v>
       </c>
       <c r="M17" s="15">
-        <v>59.183673469387</v>
+        <v>65.384615384615</v>
       </c>
       <c r="N17" s="15">
-        <v>6.849315068493</v>
+        <v>13.157894736842</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
         <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
         <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>-30.769230769230</v>
+        <v>-25</v>
       </c>
       <c r="I18" s="14">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J18" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K18" s="15">
-        <v>68.571428571428</v>
+        <v>69.444444444444</v>
       </c>
       <c r="L18" s="15">
-        <v>5.357142857142</v>
+        <v>3.389830508474</v>
       </c>
       <c r="M18" s="15">
-        <v>22.916666666666</v>
+        <v>17.307692307692</v>
       </c>
       <c r="N18" s="15">
-        <v>-76.209677419354</v>
+        <v>-77.655677655677</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>16</v>
+      </c>
+      <c r="D19" s="14">
         <v>14</v>
       </c>
-      <c r="D19" s="14">
-        <v>12</v>
-      </c>
       <c r="E19" s="15">
-        <v>16.666666666666</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F19" s="14">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G19" s="14">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H19" s="15">
-        <v>25.641025641025</v>
+        <v>17.777777777777</v>
       </c>
       <c r="I19" s="14">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="J19" s="14">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="K19" s="15">
-        <v>4.455445544554</v>
+        <v>5.555555555555</v>
       </c>
       <c r="L19" s="15">
-        <v>-5.803571428571</v>
+        <v>-5.394190871369</v>
       </c>
       <c r="M19" s="15">
-        <v>31.875</v>
+        <v>34.911242603550</v>
       </c>
       <c r="N19" s="15">
-        <v>-53.111111111111</v>
+        <v>-53.182751540041</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1125,13 +1125,13 @@
         <v>-40</v>
       </c>
       <c r="L20" s="15">
-        <v>-70</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="M20" s="15">
         <v>-25</v>
       </c>
       <c r="N20" s="15">
-        <v>-97.272727272727</v>
+        <v>-97.435897435897</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E21" s="18">
-        <v>8.333333333333</v>
+        <v>-3.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G21" s="17">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="H21" s="18">
-        <v>0</v>
+        <v>-2.803738317757</v>
       </c>
       <c r="I21" s="17">
-        <v>405</v>
+        <v>435</v>
       </c>
       <c r="J21" s="17">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="K21" s="18">
-        <v>12.5</v>
+        <v>11.538461538461</v>
       </c>
       <c r="L21" s="18">
-        <v>3.580562659846</v>
+        <v>4.567307692307</v>
       </c>
       <c r="M21" s="18">
-        <v>39.175257731958</v>
+        <v>41.233766233766</v>
       </c>
       <c r="N21" s="18">
-        <v>-63.348416289592</v>
+        <v>-63.352990732940</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,13 +1180,13 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>4</v>
-      </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>300</v>
+        <v>2</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
         <v>7</v>
@@ -1198,19 +1198,19 @@
         <v>250</v>
       </c>
       <c r="I22" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J22" s="14">
         <v>18</v>
       </c>
       <c r="K22" s="15">
-        <v>44.444444444444</v>
+        <v>55.555555555555</v>
       </c>
       <c r="L22" s="15">
-        <v>85.714285714285</v>
+        <v>75</v>
       </c>
       <c r="M22" s="15">
-        <v>116.666666666667</v>
+        <v>86.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,35 +1220,35 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
+        <v>2</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
         <v>2</v>
       </c>
       <c r="G23" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I23" s="14">
         <v>16</v>
       </c>
       <c r="J23" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K23" s="15">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L23" s="15">
-        <v>-5.882352941176</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M23" s="15">
         <v>33.333333333333</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D24" s="14">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E24" s="15">
-        <v>18.75</v>
+        <v>-12.5</v>
       </c>
       <c r="F24" s="14">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="G24" s="14">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H24" s="15">
-        <v>-16.279069767441</v>
+        <v>-10.227272727272</v>
       </c>
       <c r="I24" s="14">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="J24" s="14">
-        <v>370</v>
+        <v>394</v>
       </c>
       <c r="K24" s="15">
-        <v>-9.729729729729</v>
+        <v>-9.898477157360</v>
       </c>
       <c r="L24" s="15">
-        <v>-12.565445026178</v>
+        <v>-11.910669975186</v>
       </c>
       <c r="M24" s="15">
-        <v>0.300300300300</v>
+        <v>-0.280898876404</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>11</v>
       </c>
       <c r="D25" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E25" s="15">
-        <v>-35.294117647058</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="F25" s="14">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G25" s="14">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H25" s="15">
-        <v>-41.428571428571</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="I25" s="14">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="J25" s="14">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="K25" s="15">
-        <v>-21.863799283154</v>
+        <v>-22.558922558922</v>
       </c>
       <c r="L25" s="15">
-        <v>-30.351437699680</v>
+        <v>-30.722891566265</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E26" s="15">
-        <v>-45.454545454545</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="F26" s="14">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G26" s="14">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H26" s="15">
-        <v>-8.108108108108</v>
+        <v>-23.255813953488</v>
       </c>
       <c r="I26" s="14">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="J26" s="14">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="K26" s="15">
-        <v>-13.669064748201</v>
+        <v>-17.105263157894</v>
       </c>
       <c r="L26" s="15">
-        <v>-10.447761194029</v>
+        <v>-10.638297872340</v>
       </c>
       <c r="M26" s="15">
-        <v>50</v>
+        <v>51.807228915662</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I27" s="14">
         <v>10</v>
       </c>
       <c r="J27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>66.666666666666</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L27" s="15">
         <v>25</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G28" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>37.5</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I28" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J28" s="14">
         <v>20</v>
       </c>
       <c r="K28" s="15">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="L28" s="15">
-        <v>36</v>
+        <v>38.461538461538</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1610,29 +1610,29 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
+      <c r="G33" s="14">
+        <v>1</v>
+      </c>
+      <c r="H33" s="15">
+        <v>-100</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" s="13" t="s">
-        <v>21</v>
+      <c r="J33" s="14">
+        <v>1</v>
+      </c>
+      <c r="K33" s="15">
+        <v>-100</v>
       </c>
       <c r="L33" s="15">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-005pct.xlsx
+++ b/data/source/weekly/cs-en-us-005pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -854,17 +854,17 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="15">
         <v>-100</v>
@@ -873,7 +873,7 @@
         <v>20</v>
       </c>
       <c r="J14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="15">
         <v>-100</v>
@@ -892,14 +892,14 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>3</v>
+      </c>
+      <c r="D16" s="14">
         <v>2</v>
       </c>
-      <c r="D16" s="14">
-        <v>4</v>
-      </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="F16" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H16" s="15">
-        <v>-31.578947368421</v>
+        <v>-31.25</v>
       </c>
       <c r="I16" s="14">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J16" s="14">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K16" s="15">
-        <v>-5.555555555555</v>
+        <v>-3.571428571428</v>
       </c>
       <c r="L16" s="15">
-        <v>45.714285714285</v>
+        <v>50</v>
       </c>
       <c r="M16" s="15">
-        <v>82.142857142857</v>
+        <v>86.206896551724</v>
       </c>
       <c r="N16" s="15">
-        <v>-77.631578947368</v>
+        <v>-77.868852459016</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>-20</v>
+        <v>100</v>
       </c>
       <c r="F17" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G17" s="14">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="H17" s="15">
-        <v>-3.703703703703</v>
+        <v>42.105263157894</v>
       </c>
       <c r="I17" s="14">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="J17" s="14">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K17" s="15">
-        <v>21.126760563380</v>
+        <v>24.324324324324</v>
       </c>
       <c r="L17" s="15">
-        <v>26.470588235294</v>
+        <v>27.777777777777</v>
       </c>
       <c r="M17" s="15">
-        <v>65.384615384615</v>
+        <v>70.370370370370</v>
       </c>
       <c r="N17" s="15">
-        <v>13.157894736842</v>
+        <v>10.843373493975</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D18" s="14">
         <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F18" s="14">
+        <v>15</v>
+      </c>
+      <c r="G18" s="14">
         <v>9</v>
       </c>
-      <c r="G18" s="14">
-        <v>12</v>
-      </c>
       <c r="H18" s="15">
-        <v>-25</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="J18" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K18" s="15">
-        <v>69.444444444444</v>
+        <v>81.081081081081</v>
       </c>
       <c r="L18" s="15">
-        <v>3.389830508474</v>
+        <v>8.064516129032</v>
       </c>
       <c r="M18" s="15">
-        <v>17.307692307692</v>
+        <v>21.818181818181</v>
       </c>
       <c r="N18" s="15">
-        <v>-77.655677655677</v>
+        <v>-76.325088339222</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>9</v>
+      </c>
+      <c r="D19" s="14">
         <v>16</v>
       </c>
-      <c r="D19" s="14">
-        <v>14</v>
-      </c>
       <c r="E19" s="15">
-        <v>14.285714285714</v>
+        <v>-43.75</v>
       </c>
       <c r="F19" s="14">
         <v>53</v>
       </c>
       <c r="G19" s="14">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="H19" s="15">
-        <v>17.777777777777</v>
+        <v>-7.017543859649</v>
       </c>
       <c r="I19" s="14">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="J19" s="14">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="K19" s="15">
-        <v>5.555555555555</v>
+        <v>2.586206896551</v>
       </c>
       <c r="L19" s="15">
-        <v>-5.394190871369</v>
+        <v>-6.299212598425</v>
       </c>
       <c r="M19" s="15">
-        <v>34.911242603550</v>
+        <v>36.781609195402</v>
       </c>
       <c r="N19" s="15">
-        <v>-53.182751540041</v>
+        <v>-54.054054054054</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1106,8 +1106,8 @@
       <c r="E20" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="14">
-        <v>2</v>
+      <c r="F20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>20</v>
@@ -1128,10 +1128,10 @@
         <v>-72.727272727272</v>
       </c>
       <c r="M20" s="15">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="N20" s="15">
-        <v>-97.435897435897</v>
+        <v>-97.5</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D21" s="17">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E21" s="18">
-        <v>-3.333333333333</v>
+        <v>4.347826086956</v>
       </c>
       <c r="F21" s="17">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G21" s="17">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H21" s="18">
-        <v>-2.803738317757</v>
+        <v>0.943396226415</v>
       </c>
       <c r="I21" s="17">
-        <v>435</v>
+        <v>460</v>
       </c>
       <c r="J21" s="17">
-        <v>390</v>
+        <v>413</v>
       </c>
       <c r="K21" s="18">
-        <v>11.538461538461</v>
+        <v>11.380145278450</v>
       </c>
       <c r="L21" s="18">
-        <v>4.567307692307</v>
+        <v>5.263157894736</v>
       </c>
       <c r="M21" s="18">
-        <v>41.233766233766</v>
+        <v>43.75</v>
       </c>
       <c r="N21" s="18">
-        <v>-63.352990732940</v>
+        <v>-63.317384370016</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>2</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>250</v>
       </c>
       <c r="I22" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J22" s="14">
         <v>18</v>
       </c>
       <c r="K22" s="15">
-        <v>55.555555555555</v>
+        <v>61.111111111111</v>
       </c>
       <c r="L22" s="15">
-        <v>75</v>
+        <v>61.111111111111</v>
       </c>
       <c r="M22" s="15">
-        <v>86.666666666666</v>
+        <v>81.25</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>1</v>
       </c>
       <c r="D23" s="14">
         <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F23" s="14">
         <v>2</v>
       </c>
       <c r="G23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H23" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="I23" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J23" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K23" s="15">
-        <v>-11.111111111111</v>
+        <v>-15</v>
       </c>
       <c r="L23" s="15">
-        <v>-11.111111111111</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="M23" s="15">
-        <v>33.333333333333</v>
+        <v>41.666666666666</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D24" s="14">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E24" s="15">
-        <v>-12.5</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="F24" s="14">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G24" s="14">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H24" s="15">
-        <v>-10.227272727272</v>
+        <v>3.896103896103</v>
       </c>
       <c r="I24" s="14">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="J24" s="14">
-        <v>394</v>
+        <v>411</v>
       </c>
       <c r="K24" s="15">
-        <v>-9.898477157360</v>
+        <v>-10.218978102189</v>
       </c>
       <c r="L24" s="15">
-        <v>-11.910669975186</v>
+        <v>-14.976958525345</v>
       </c>
       <c r="M24" s="15">
-        <v>-0.280898876404</v>
+        <v>-3.655352480417</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D25" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E25" s="15">
-        <v>-38.888888888888</v>
+        <v>-40</v>
       </c>
       <c r="F25" s="14">
         <v>48</v>
       </c>
       <c r="G25" s="14">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H25" s="15">
-        <v>-29.411764705882</v>
+        <v>-26.153846153846</v>
       </c>
       <c r="I25" s="14">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="J25" s="14">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="K25" s="15">
-        <v>-22.558922558922</v>
+        <v>-23.397435897435</v>
       </c>
       <c r="L25" s="15">
-        <v>-30.722891566265</v>
+        <v>-33.053221288515</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>-53.846153846153</v>
+        <v>60</v>
       </c>
       <c r="F26" s="14">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G26" s="14">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H26" s="15">
-        <v>-23.255813953488</v>
+        <v>-23.684210526315</v>
       </c>
       <c r="I26" s="14">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="J26" s="14">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="K26" s="15">
-        <v>-17.105263157894</v>
+        <v>-14.649681528662</v>
       </c>
       <c r="L26" s="15">
-        <v>-10.638297872340</v>
+        <v>-9.459459459459</v>
       </c>
       <c r="M26" s="15">
-        <v>51.807228915662</v>
+        <v>45.652173913043</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
         <v>10</v>
       </c>
       <c r="J27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K27" s="15">
-        <v>42.857142857142</v>
+        <v>25</v>
       </c>
       <c r="L27" s="15">
-        <v>25</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>42.857142857142</v>
+        <v>100</v>
       </c>
       <c r="I28" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J28" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K28" s="15">
-        <v>80</v>
+        <v>72.727272727272</v>
       </c>
       <c r="L28" s="15">
-        <v>38.461538461538</v>
+        <v>35.714285714285</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,29 +1469,29 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>-100</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>21</v>
+      <c r="J29" s="14">
+        <v>1</v>
+      </c>
+      <c r="K29" s="15">
+        <v>-100</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
@@ -1510,29 +1510,29 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>-100</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>21</v>
+      <c r="J30" s="14">
+        <v>1</v>
+      </c>
+      <c r="K30" s="15">
+        <v>-100</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
@@ -1576,7 +1576,7 @@
         <v>-83.333333333333</v>
       </c>
       <c r="L31" s="15">
-        <v>-88.888888888888</v>
+        <v>-90</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
